--- a/Iteration 2/Agile Gantt chart .xlsx
+++ b/Iteration 2/Agile Gantt chart .xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="916" documentId="8_{5FCFFA2A-1C94-4F30-8EBC-885A9A0A3AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA54B23A-657F-48AB-B515-C65E66D4E772}"/>
+  <xr:revisionPtr revIDLastSave="1079" documentId="8_{5FCFFA2A-1C94-4F30-8EBC-885A9A0A3AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD63781A-8482-45A3-BE50-53AAA5CFEE05}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="415" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="91">
   <si>
     <t>Task 3</t>
   </si>
@@ -309,6 +309,30 @@
   </si>
   <si>
     <t>Complete all tasks for Iteration 2 and submit Progress Reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete all tasks for Iteration 3 in a GitHub repository </t>
+  </si>
+  <si>
+    <t>Push website files to the GitHub Repository</t>
+  </si>
+  <si>
+    <t>Publish Website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting #3 </t>
+  </si>
+  <si>
+    <t>Push Risk Register and add relevant risks relating to the project</t>
+  </si>
+  <si>
+    <t>Rearrange GitHub Repository (website to /docs), check integration</t>
+  </si>
+  <si>
+    <t>Push User Acceptance Test Results and add from notes</t>
+  </si>
+  <si>
+    <t>Update README file with Iteration 3 details</t>
   </si>
 </sst>
 </file>
@@ -1285,6 +1309,9 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1335,9 +1362,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -2647,75 +2671,6 @@
       </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <color auto="1"/>
       </font>
@@ -2840,6 +2795,75 @@
         <bottom style="thin">
           <color theme="0"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3593,7 +3617,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="39" fmlaLink="$C$7" horiz="1" max="365" page="2" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="39" fmlaLink="$C$7" horiz="1" max="365" page="2" val="30"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3945,13 +3969,9 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9DCD786-338F-4F4D-899D-936CC39D523A}" name="Milestones435263" displayName="Milestones435263" ref="B9:G41" totalsRowShown="0" headerRowDxfId="126" dataDxfId="125">
-  <autoFilter ref="B9:G41" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9DCD786-338F-4F4D-899D-936CC39D523A}" name="Milestones435263" displayName="Milestones435263" ref="B9:G54" totalsRowShown="0" headerRowDxfId="126" dataDxfId="125">
+  <autoFilter ref="B9:G54" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4364,11 +4384,11 @@
     <row r="2" spans="1:13" ht="50.15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="7"/>
       <c r="B2" s="107"/>
-      <c r="C2" s="137" t="s">
+      <c r="C2" s="138" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
       <c r="F2" s="107"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -4396,11 +4416,11 @@
     <row r="4" spans="1:13" s="8" customFormat="1" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="7"/>
       <c r="B4" s="102"/>
-      <c r="C4" s="138" t="s">
+      <c r="C4" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
       <c r="F4" s="102"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -4413,11 +4433,11 @@
     <row r="5" spans="1:13" s="8" customFormat="1" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A5" s="7"/>
       <c r="B5" s="102"/>
-      <c r="C5" s="138" t="s">
+      <c r="C5" s="139" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="138"/>
-      <c r="E5" s="138"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="139"/>
       <c r="F5" s="102"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -4517,7 +4537,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BP43"/>
+  <dimension ref="A1:BP56"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.7265625" style="9" customWidth="1"/>
@@ -4535,27 +4555,27 @@
     <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10"/>
-      <c r="B2" s="131" t="s">
+      <c r="B2" s="132" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="133"/>
-      <c r="P2" s="133"/>
-      <c r="Q2" s="133"/>
-      <c r="R2" s="133"/>
-      <c r="S2" s="133"/>
-      <c r="T2" s="133"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="134"/>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="134"/>
+      <c r="S2" s="134"/>
+      <c r="T2" s="134"/>
       <c r="U2" s="61"/>
       <c r="V2" s="61"/>
       <c r="W2" s="61"/>
@@ -4629,36 +4649,36 @@
         <v>18</v>
       </c>
       <c r="H4" s="69"/>
-      <c r="I4" s="134" t="s">
+      <c r="I4" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="134"/>
-      <c r="N4" s="135" t="s">
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="N4" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="135"/>
-      <c r="P4" s="135"/>
-      <c r="Q4" s="135"/>
-      <c r="S4" s="136" t="s">
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="S4" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="T4" s="136"/>
-      <c r="U4" s="136"/>
-      <c r="V4" s="136"/>
-      <c r="X4" s="129" t="s">
+      <c r="T4" s="137"/>
+      <c r="U4" s="137"/>
+      <c r="V4" s="137"/>
+      <c r="X4" s="130" t="s">
         <v>28</v>
       </c>
-      <c r="Y4" s="129"/>
-      <c r="Z4" s="129"/>
-      <c r="AA4" s="129"/>
-      <c r="AC4" s="130" t="s">
+      <c r="Y4" s="130"/>
+      <c r="Z4" s="130"/>
+      <c r="AA4" s="130"/>
+      <c r="AC4" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="AD4" s="130"/>
-      <c r="AE4" s="130"/>
-      <c r="AF4" s="130"/>
+      <c r="AD4" s="131"/>
+      <c r="AE4" s="131"/>
+      <c r="AF4" s="131"/>
     </row>
     <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
@@ -4687,7 +4707,7 @@
       <c r="H6" s="69"/>
       <c r="I6" s="85" t="str">
         <f ca="1">TEXT(I7,"mmmm")</f>
-        <v>February</v>
+        <v>March</v>
       </c>
       <c r="J6" s="85"/>
       <c r="K6" s="85"/>
@@ -4697,7 +4717,7 @@
       <c r="O6" s="85"/>
       <c r="P6" s="85" t="str">
         <f ca="1">IF(TEXT(P7,"mmmm")=I6,"",TEXT(P7,"mmmm"))</f>
-        <v>March</v>
+        <v>April</v>
       </c>
       <c r="Q6" s="85"/>
       <c r="R6" s="85"/>
@@ -4737,7 +4757,7 @@
       <c r="AQ6" s="85"/>
       <c r="AR6" s="85" t="str">
         <f ca="1">IF(OR(TEXT(AR7,"mmmm")=AK6,TEXT(AR7,"mmmm")=AD6,TEXT(AR7,"mmmm")=W6,TEXT(AR7,"mmmm")=P6),"",TEXT(AR7,"mmmm"))</f>
-        <v>April</v>
+        <v>May</v>
       </c>
       <c r="AS6" s="85"/>
       <c r="AT6" s="85"/>
@@ -4772,7 +4792,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="76">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D7" s="68"/>
       <c r="E7" s="69"/>
@@ -4781,227 +4801,227 @@
       <c r="H7" s="77"/>
       <c r="I7" s="92">
         <f ca="1">IFERROR(Project_Start+Scrolling_Increment,TODAY())</f>
-        <v>46078</v>
+        <v>46108</v>
       </c>
       <c r="J7" s="93">
         <f ca="1">I7+1</f>
-        <v>46079</v>
+        <v>46109</v>
       </c>
       <c r="K7" s="93">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46080</v>
+        <v>46110</v>
       </c>
       <c r="L7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46081</v>
+        <v>46111</v>
       </c>
       <c r="M7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46082</v>
+        <v>46112</v>
       </c>
       <c r="N7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46083</v>
+        <v>46113</v>
       </c>
       <c r="O7" s="94">
         <f t="shared" ca="1" si="0"/>
-        <v>46084</v>
+        <v>46114</v>
       </c>
       <c r="P7" s="93">
         <f ca="1">O7+1</f>
-        <v>46085</v>
+        <v>46115</v>
       </c>
       <c r="Q7" s="93">
         <f ca="1">P7+1</f>
-        <v>46086</v>
+        <v>46116</v>
       </c>
       <c r="R7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46087</v>
+        <v>46117</v>
       </c>
       <c r="S7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46088</v>
+        <v>46118</v>
       </c>
       <c r="T7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46089</v>
+        <v>46119</v>
       </c>
       <c r="U7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46090</v>
+        <v>46120</v>
       </c>
       <c r="V7" s="94">
         <f t="shared" ca="1" si="0"/>
-        <v>46091</v>
+        <v>46121</v>
       </c>
       <c r="W7" s="93">
         <f ca="1">V7+1</f>
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="X7" s="93">
         <f ca="1">W7+1</f>
-        <v>46093</v>
+        <v>46123</v>
       </c>
       <c r="Y7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46094</v>
+        <v>46124</v>
       </c>
       <c r="Z7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46095</v>
+        <v>46125</v>
       </c>
       <c r="AA7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46096</v>
+        <v>46126</v>
       </c>
       <c r="AB7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46097</v>
+        <v>46127</v>
       </c>
       <c r="AC7" s="94">
         <f t="shared" ca="1" si="0"/>
-        <v>46098</v>
+        <v>46128</v>
       </c>
       <c r="AD7" s="93">
         <f ca="1">AC7+1</f>
-        <v>46099</v>
+        <v>46129</v>
       </c>
       <c r="AE7" s="93">
         <f ca="1">AD7+1</f>
-        <v>46100</v>
+        <v>46130</v>
       </c>
       <c r="AF7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46101</v>
+        <v>46131</v>
       </c>
       <c r="AG7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46102</v>
+        <v>46132</v>
       </c>
       <c r="AH7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46103</v>
+        <v>46133</v>
       </c>
       <c r="AI7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46104</v>
+        <v>46134</v>
       </c>
       <c r="AJ7" s="94">
         <f t="shared" ca="1" si="0"/>
-        <v>46105</v>
+        <v>46135</v>
       </c>
       <c r="AK7" s="93">
         <f ca="1">AJ7+1</f>
-        <v>46106</v>
+        <v>46136</v>
       </c>
       <c r="AL7" s="93">
         <f ca="1">AK7+1</f>
-        <v>46107</v>
+        <v>46137</v>
       </c>
       <c r="AM7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46108</v>
+        <v>46138</v>
       </c>
       <c r="AN7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46109</v>
+        <v>46139</v>
       </c>
       <c r="AO7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46110</v>
+        <v>46140</v>
       </c>
       <c r="AP7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46111</v>
+        <v>46141</v>
       </c>
       <c r="AQ7" s="94">
         <f t="shared" ca="1" si="0"/>
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="AR7" s="93">
         <f ca="1">AQ7+1</f>
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="AS7" s="93">
         <f ca="1">AR7+1</f>
-        <v>46114</v>
+        <v>46144</v>
       </c>
       <c r="AT7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46115</v>
+        <v>46145</v>
       </c>
       <c r="AU7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46116</v>
+        <v>46146</v>
       </c>
       <c r="AV7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46117</v>
+        <v>46147</v>
       </c>
       <c r="AW7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="AX7" s="94">
         <f t="shared" ca="1" si="0"/>
-        <v>46119</v>
+        <v>46149</v>
       </c>
       <c r="AY7" s="93">
         <f ca="1">AX7+1</f>
-        <v>46120</v>
+        <v>46150</v>
       </c>
       <c r="AZ7" s="93">
         <f ca="1">AY7+1</f>
-        <v>46121</v>
+        <v>46151</v>
       </c>
       <c r="BA7" s="93">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46122</v>
+        <v>46152</v>
       </c>
       <c r="BB7" s="93">
         <f t="shared" ca="1" si="1"/>
-        <v>46123</v>
+        <v>46153</v>
       </c>
       <c r="BC7" s="93">
         <f t="shared" ca="1" si="1"/>
-        <v>46124</v>
+        <v>46154</v>
       </c>
       <c r="BD7" s="93">
         <f t="shared" ca="1" si="1"/>
-        <v>46125</v>
+        <v>46155</v>
       </c>
       <c r="BE7" s="94">
         <f t="shared" ca="1" si="1"/>
-        <v>46126</v>
+        <v>46156</v>
       </c>
       <c r="BF7" s="93">
         <f ca="1">BE7+1</f>
-        <v>46127</v>
+        <v>46157</v>
       </c>
       <c r="BG7" s="93">
         <f ca="1">BF7+1</f>
-        <v>46128</v>
+        <v>46158</v>
       </c>
       <c r="BH7" s="93">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46129</v>
+        <v>46159</v>
       </c>
       <c r="BI7" s="93">
         <f t="shared" ca="1" si="2"/>
-        <v>46130</v>
+        <v>46160</v>
       </c>
       <c r="BJ7" s="93">
         <f t="shared" ca="1" si="2"/>
-        <v>46131</v>
+        <v>46161</v>
       </c>
       <c r="BK7" s="93">
         <f t="shared" ca="1" si="2"/>
-        <v>46132</v>
+        <v>46162</v>
       </c>
       <c r="BL7" s="94">
         <f t="shared" ca="1" si="2"/>
-        <v>46133</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -5093,27 +5113,27 @@
       <c r="H9" s="82"/>
       <c r="I9" s="100" t="str">
         <f t="shared" ref="I9:BL9" ca="1" si="3">LEFT(TEXT(I7,"ddd"),1)</f>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="J9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="K9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="L9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="M9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="N9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="O9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -5121,27 +5141,27 @@
       </c>
       <c r="P9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="Q9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="R9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="S9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="T9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="U9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="V9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -5149,27 +5169,27 @@
       </c>
       <c r="W9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="X9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="Y9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="Z9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AA9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="AB9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="AC9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -5177,27 +5197,27 @@
       </c>
       <c r="AD9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="AE9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="AF9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AG9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AH9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="AI9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="AJ9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -5205,27 +5225,27 @@
       </c>
       <c r="AK9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="AL9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="AM9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AN9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AO9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="AP9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="AQ9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -5233,27 +5253,27 @@
       </c>
       <c r="AR9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="AS9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="AT9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="AU9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AV9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="AW9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="AX9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -5261,27 +5281,27 @@
       </c>
       <c r="AY9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="AZ9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="BA9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="BB9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BC9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="BD9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="BE9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -5289,27 +5309,27 @@
       </c>
       <c r="BF9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>F</v>
       </c>
       <c r="BG9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>S</v>
       </c>
       <c r="BH9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>S</v>
       </c>
       <c r="BI9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="BJ9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="BK9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>W</v>
       </c>
       <c r="BL9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -5638,9 +5658,9 @@
         <v>1</v>
       </c>
       <c r="H12" s="53"/>
-      <c r="I12" s="22">
+      <c r="I12" s="22" t="str">
         <f ca="1">IF(AND($C12="Goal",I$7&gt;=$F12,I$7&lt;=$F12+$G12-1),2,IF(AND($C12="Milestone",I$7&gt;=$F12,I$7&lt;=$F12+$G12-1),1,""))</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="J12" s="22" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -5884,9 +5904,9 @@
         <v>1</v>
       </c>
       <c r="H13" s="53"/>
-      <c r="I13" s="22">
+      <c r="I13" s="22" t="str">
         <f t="shared" ref="I13:X28" ca="1" si="8">IF(AND($C13="Goal",I$7&gt;=$F13,I$7&lt;=$F13+$G13-1),2,IF(AND($C13="Milestone",I$7&gt;=$F13,I$7&lt;=$F13+$G13-1),1,""))</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="J13" s="22" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -6404,9 +6424,9 @@
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="P15" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+      <c r="P15" s="22" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="Q15" s="22" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -6920,9 +6940,9 @@
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="V17" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+      <c r="V17" s="22" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="W17" s="22" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -7908,9 +7928,9 @@
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
-      <c r="W21" s="22">
-        <f t="shared" ca="1" si="4"/>
-        <v>2</v>
+      <c r="W21" s="22" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
       </c>
       <c r="X21" s="22" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -8182,9 +8202,9 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="AD22" s="22">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+      <c r="AD22" s="22" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
       </c>
       <c r="AE22" s="22" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8664,9 +8684,9 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="AD24" s="22">
-        <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+      <c r="AD24" s="22" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
       </c>
       <c r="AE24" s="22" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -8910,9 +8930,9 @@
         <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
-      <c r="AD25" s="22">
-        <f t="shared" ca="1" si="5"/>
-        <v>2</v>
+      <c r="AD25" s="22" t="str">
+        <f t="shared" ca="1" si="5"/>
+        <v/>
       </c>
       <c r="AE25" s="22" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -9197,7 +9217,7 @@
         <v/>
       </c>
       <c r="AN26" s="22" t="str">
-        <f t="shared" ref="AN26:BC34" ca="1" si="9">IF(AND($C26="Goal",AN$7&gt;=$F26,AN$7&lt;=$F26+$G26-1),2,IF(AND($C26="Milestone",AN$7&gt;=$F26,AN$7&lt;=$F26+$G26-1),1,""))</f>
+        <f t="shared" ref="AN26:BC41" ca="1" si="9">IF(AND($C26="Goal",AN$7&gt;=$F26,AN$7&lt;=$F26+$G26-1),2,IF(AND($C26="Milestone",AN$7&gt;=$F26,AN$7&lt;=$F26+$G26-1),1,""))</f>
         <v/>
       </c>
       <c r="AO26" s="22" t="str">
@@ -9261,7 +9281,7 @@
         <v/>
       </c>
       <c r="BD26" s="22" t="str">
-        <f t="shared" ref="BD26:BL34" ca="1" si="10">IF(AND($C26="Goal",BD$7&gt;=$F26,BD$7&lt;=$F26+$G26-1),2,IF(AND($C26="Milestone",BD$7&gt;=$F26,BD$7&lt;=$F26+$G26-1),1,""))</f>
+        <f t="shared" ref="BD26:BL53" ca="1" si="10">IF(AND($C26="Goal",BD$7&gt;=$F26,BD$7&lt;=$F26+$G26-1),2,IF(AND($C26="Milestone",BD$7&gt;=$F26,BD$7&lt;=$F26+$G26-1),1,""))</f>
         <v/>
       </c>
       <c r="BE26" s="22" t="str">
@@ -9383,7 +9403,7 @@
         <v/>
       </c>
       <c r="Y27" s="22" t="str">
-        <f t="shared" ref="Y27:AM34" ca="1" si="11">IF(AND($C27="Goal",Y$7&gt;=$F27,Y$7&lt;=$F27+$G27-1),2,IF(AND($C27="Milestone",Y$7&gt;=$F27,Y$7&lt;=$F27+$G27-1),1,""))</f>
+        <f t="shared" ref="Y27:AM42" ca="1" si="11">IF(AND($C27="Goal",Y$7&gt;=$F27,Y$7&lt;=$F27+$G27-1),2,IF(AND($C27="Milestone",Y$7&gt;=$F27,Y$7&lt;=$F27+$G27-1),1,""))</f>
         <v/>
       </c>
       <c r="Z27" s="22" t="str">
@@ -9430,9 +9450,9 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="AK27" s="22">
-        <f t="shared" ca="1" si="11"/>
-        <v>2</v>
+      <c r="AK27" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
       </c>
       <c r="AL27" s="22" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -9811,7 +9831,7 @@
       </c>
       <c r="H29" s="53"/>
       <c r="I29" s="22" t="str">
-        <f t="shared" ref="I29:X34" ca="1" si="12">IF(AND($C29="Goal",I$7&gt;=$F29,I$7&lt;=$F29+$G29-1),2,IF(AND($C29="Milestone",I$7&gt;=$F29,I$7&lt;=$F29+$G29-1),1,""))</f>
+        <f t="shared" ref="I29:X43" ca="1" si="12">IF(AND($C29="Goal",I$7&gt;=$F29,I$7&lt;=$F29+$G29-1),2,IF(AND($C29="Milestone",I$7&gt;=$F29,I$7&lt;=$F29+$G29-1),1,""))</f>
         <v/>
       </c>
       <c r="J29" s="22" t="str">
@@ -10076,9 +10096,9 @@
         <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
-      <c r="N30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
+      <c r="N30" s="22">
+        <f t="shared" ca="1" si="12"/>
+        <v>2</v>
       </c>
       <c r="O30" s="22" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -10196,9 +10216,9 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="AR30" s="22">
-        <f t="shared" ca="1" si="9"/>
-        <v>2</v>
+      <c r="AR30" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
       </c>
       <c r="AS30" s="22" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -10650,9 +10670,9 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="AI32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
+      <c r="AI32" s="22">
+        <f t="shared" ca="1" si="11"/>
+        <v>2</v>
       </c>
       <c r="AJ32" s="22" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -10771,7 +10791,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9"/>
       <c r="B33" s="12" t="s">
         <v>69</v>
@@ -11017,7 +11037,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9"/>
       <c r="B34" s="12" t="s">
         <v>66</v>
@@ -11263,7 +11283,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9"/>
       <c r="B35" s="57" t="s">
         <v>62</v>
@@ -11284,64 +11304,232 @@
         <v>8</v>
       </c>
       <c r="H35" s="53"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="22"/>
-      <c r="O35" s="22"/>
-      <c r="P35" s="22"/>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="22"/>
-      <c r="S35" s="22"/>
-      <c r="T35" s="22"/>
-      <c r="U35" s="22"/>
-      <c r="V35" s="22"/>
-      <c r="W35" s="22"/>
-      <c r="X35" s="22"/>
-      <c r="Y35" s="22"/>
-      <c r="Z35" s="22"/>
-      <c r="AA35" s="22"/>
-      <c r="AB35" s="22"/>
-      <c r="AC35" s="22"/>
-      <c r="AD35" s="22"/>
-      <c r="AE35" s="22"/>
-      <c r="AF35" s="22"/>
-      <c r="AG35" s="22"/>
-      <c r="AH35" s="22"/>
-      <c r="AI35" s="22"/>
-      <c r="AJ35" s="22"/>
-      <c r="AK35" s="22"/>
-      <c r="AL35" s="22"/>
-      <c r="AM35" s="22"/>
-      <c r="AN35" s="22"/>
-      <c r="AO35" s="22"/>
-      <c r="AP35" s="22"/>
-      <c r="AQ35" s="22"/>
-      <c r="AR35" s="22"/>
-      <c r="AS35" s="22"/>
-      <c r="AT35" s="22"/>
-      <c r="AU35" s="22"/>
-      <c r="AV35" s="22"/>
-      <c r="AW35" s="22"/>
-      <c r="AX35" s="22"/>
-      <c r="AY35" s="22"/>
-      <c r="AZ35" s="22"/>
-      <c r="BA35" s="22"/>
-      <c r="BB35" s="22"/>
-      <c r="BC35" s="22"/>
-      <c r="BD35" s="22"/>
-      <c r="BE35" s="22"/>
-      <c r="BF35" s="22"/>
-      <c r="BG35" s="22"/>
-      <c r="BH35" s="22"/>
-      <c r="BI35" s="22"/>
-      <c r="BJ35" s="22"/>
-      <c r="BK35" s="22"/>
-      <c r="BL35" s="22"/>
+      <c r="I35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="J35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="K35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="L35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="M35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="N35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="O35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="P35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Q35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="R35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="S35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="T35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="U35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="V35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="W35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="X35" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Y35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="Z35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AA35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AB35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AC35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AD35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AE35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AF35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AG35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AH35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AI35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AJ35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AK35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AL35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AM35" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AN35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AO35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AP35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AQ35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AR35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AS35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AT35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AU35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AV35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AW35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AX35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AY35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AZ35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BA35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BB35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BC35" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BD35" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE35" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF35" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG35" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH35" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI35" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ35" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK35" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL35" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
     </row>
-    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9"/>
       <c r="B36" s="57" t="s">
         <v>67</v>
@@ -11362,64 +11550,232 @@
         <v>8</v>
       </c>
       <c r="H36" s="53"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="22"/>
-      <c r="N36" s="22"/>
-      <c r="O36" s="22"/>
-      <c r="P36" s="22"/>
-      <c r="Q36" s="22"/>
-      <c r="R36" s="22"/>
-      <c r="S36" s="22"/>
-      <c r="T36" s="22"/>
-      <c r="U36" s="22"/>
-      <c r="V36" s="22"/>
-      <c r="W36" s="22"/>
-      <c r="X36" s="22"/>
-      <c r="Y36" s="22"/>
-      <c r="Z36" s="22"/>
-      <c r="AA36" s="22"/>
-      <c r="AB36" s="22"/>
-      <c r="AC36" s="22"/>
-      <c r="AD36" s="22"/>
-      <c r="AE36" s="22"/>
-      <c r="AF36" s="22"/>
-      <c r="AG36" s="22"/>
-      <c r="AH36" s="22"/>
-      <c r="AI36" s="22"/>
-      <c r="AJ36" s="22"/>
-      <c r="AK36" s="22"/>
-      <c r="AL36" s="22"/>
-      <c r="AM36" s="22"/>
-      <c r="AN36" s="22"/>
-      <c r="AO36" s="22"/>
-      <c r="AP36" s="22"/>
-      <c r="AQ36" s="22"/>
-      <c r="AR36" s="22"/>
-      <c r="AS36" s="22"/>
-      <c r="AT36" s="22"/>
-      <c r="AU36" s="22"/>
-      <c r="AV36" s="22"/>
-      <c r="AW36" s="22"/>
-      <c r="AX36" s="22"/>
-      <c r="AY36" s="22"/>
-      <c r="AZ36" s="22"/>
-      <c r="BA36" s="22"/>
-      <c r="BB36" s="22"/>
-      <c r="BC36" s="22"/>
-      <c r="BD36" s="22"/>
-      <c r="BE36" s="22"/>
-      <c r="BF36" s="22"/>
-      <c r="BG36" s="22"/>
-      <c r="BH36" s="22"/>
-      <c r="BI36" s="22"/>
-      <c r="BJ36" s="22"/>
-      <c r="BK36" s="22"/>
-      <c r="BL36" s="22"/>
+      <c r="I36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="J36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="K36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="L36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="M36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="N36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="O36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="P36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Q36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="R36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="S36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="T36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="U36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="V36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="W36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="X36" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Y36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="Z36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AA36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AB36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AC36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AD36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AE36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AF36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AG36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AH36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AI36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AJ36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AK36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AL36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AM36" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AN36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AO36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AP36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AQ36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AR36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AS36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AT36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AU36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AV36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AW36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AX36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AY36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AZ36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BA36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BB36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BC36" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BD36" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE36" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF36" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG36" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH36" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI36" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ36" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK36" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL36" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
     </row>
-    <row r="37" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9"/>
       <c r="B37" s="127" t="s">
         <v>68</v>
@@ -11440,64 +11796,232 @@
         <v>8</v>
       </c>
       <c r="H37" s="53"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="22"/>
-      <c r="O37" s="22"/>
-      <c r="P37" s="22"/>
-      <c r="Q37" s="22"/>
-      <c r="R37" s="22"/>
-      <c r="S37" s="22"/>
-      <c r="T37" s="22"/>
-      <c r="U37" s="22"/>
-      <c r="V37" s="22"/>
-      <c r="W37" s="22"/>
-      <c r="X37" s="22"/>
-      <c r="Y37" s="22"/>
-      <c r="Z37" s="22"/>
-      <c r="AA37" s="22"/>
-      <c r="AB37" s="22"/>
-      <c r="AC37" s="22"/>
-      <c r="AD37" s="22"/>
-      <c r="AE37" s="22"/>
-      <c r="AF37" s="22"/>
-      <c r="AG37" s="22"/>
-      <c r="AH37" s="22"/>
-      <c r="AI37" s="22"/>
-      <c r="AJ37" s="22"/>
-      <c r="AK37" s="22"/>
-      <c r="AL37" s="22"/>
-      <c r="AM37" s="22"/>
-      <c r="AN37" s="22"/>
-      <c r="AO37" s="22"/>
-      <c r="AP37" s="22"/>
-      <c r="AQ37" s="22"/>
-      <c r="AR37" s="22"/>
-      <c r="AS37" s="22"/>
-      <c r="AT37" s="22"/>
-      <c r="AU37" s="22"/>
-      <c r="AV37" s="22"/>
-      <c r="AW37" s="22"/>
-      <c r="AX37" s="22"/>
-      <c r="AY37" s="22"/>
-      <c r="AZ37" s="22"/>
-      <c r="BA37" s="22"/>
-      <c r="BB37" s="22"/>
-      <c r="BC37" s="22"/>
-      <c r="BD37" s="22"/>
-      <c r="BE37" s="22"/>
-      <c r="BF37" s="22"/>
-      <c r="BG37" s="22"/>
-      <c r="BH37" s="22"/>
-      <c r="BI37" s="22"/>
-      <c r="BJ37" s="22"/>
-      <c r="BK37" s="22"/>
-      <c r="BL37" s="22"/>
+      <c r="I37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="J37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="K37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="L37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="M37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="N37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="O37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="P37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Q37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="R37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="S37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="T37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="U37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="V37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="W37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="X37" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Y37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="Z37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AA37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AB37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AC37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AD37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AE37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AF37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AG37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AH37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AI37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AJ37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AK37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AL37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AM37" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AN37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AO37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AP37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AQ37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AR37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AS37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AT37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AU37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AV37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AW37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AX37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AY37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AZ37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BA37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BB37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BC37" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BD37" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE37" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF37" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG37" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH37" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI37" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ37" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK37" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL37" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
     </row>
-    <row r="38" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
       <c r="B38" s="127" t="s">
         <v>82</v>
@@ -11518,66 +12042,234 @@
         <v>1</v>
       </c>
       <c r="H38" s="53"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="22"/>
-      <c r="N38" s="22"/>
-      <c r="O38" s="22"/>
-      <c r="P38" s="22"/>
-      <c r="Q38" s="22"/>
-      <c r="R38" s="22"/>
-      <c r="S38" s="22"/>
-      <c r="T38" s="22"/>
-      <c r="U38" s="22"/>
-      <c r="V38" s="22"/>
-      <c r="W38" s="22"/>
-      <c r="X38" s="22"/>
-      <c r="Y38" s="22"/>
-      <c r="Z38" s="22"/>
-      <c r="AA38" s="22"/>
-      <c r="AB38" s="22"/>
-      <c r="AC38" s="22"/>
-      <c r="AD38" s="22"/>
-      <c r="AE38" s="22"/>
-      <c r="AF38" s="22"/>
-      <c r="AG38" s="22"/>
-      <c r="AH38" s="22"/>
-      <c r="AI38" s="22"/>
-      <c r="AJ38" s="22"/>
-      <c r="AK38" s="22"/>
-      <c r="AL38" s="22"/>
-      <c r="AM38" s="22"/>
-      <c r="AN38" s="22"/>
-      <c r="AO38" s="22"/>
-      <c r="AP38" s="22"/>
-      <c r="AQ38" s="22"/>
-      <c r="AR38" s="22"/>
-      <c r="AS38" s="22"/>
-      <c r="AT38" s="22"/>
-      <c r="AU38" s="22"/>
-      <c r="AV38" s="22"/>
-      <c r="AW38" s="22"/>
-      <c r="AX38" s="22"/>
-      <c r="AY38" s="22"/>
-      <c r="AZ38" s="22"/>
-      <c r="BA38" s="22"/>
-      <c r="BB38" s="22"/>
-      <c r="BC38" s="22"/>
-      <c r="BD38" s="22"/>
-      <c r="BE38" s="22"/>
-      <c r="BF38" s="22"/>
-      <c r="BG38" s="22"/>
-      <c r="BH38" s="22"/>
-      <c r="BI38" s="22"/>
-      <c r="BJ38" s="22"/>
-      <c r="BK38" s="22"/>
-      <c r="BL38" s="22"/>
+      <c r="I38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="J38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="K38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="L38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="M38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="N38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="O38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="P38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Q38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="R38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="S38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="T38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="U38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="V38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="W38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="X38" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Y38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="Z38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AA38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AB38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AC38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AD38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AE38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AF38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AG38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AH38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AI38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AJ38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AK38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AL38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AM38" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AN38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AO38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AP38" s="22">
+        <f t="shared" ca="1" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AQ38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AR38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AS38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AT38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AU38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AV38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AW38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AX38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AY38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AZ38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BA38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BB38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BC38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BD38" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE38" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF38" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG38" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH38" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI38" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ38" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK38" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL38" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
     </row>
-    <row r="39" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
-      <c r="B39" s="146" t="s">
+      <c r="B39" s="129" t="s">
         <v>72</v>
       </c>
       <c r="C39" s="53"/>
@@ -11586,373 +12278,3713 @@
       <c r="F39" s="55"/>
       <c r="G39" s="56"/>
       <c r="H39" s="53"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="22"/>
-      <c r="N39" s="22"/>
-      <c r="O39" s="22"/>
-      <c r="P39" s="22"/>
-      <c r="Q39" s="22"/>
-      <c r="R39" s="22"/>
-      <c r="S39" s="22"/>
-      <c r="T39" s="22"/>
-      <c r="U39" s="22"/>
-      <c r="V39" s="22"/>
-      <c r="W39" s="22"/>
-      <c r="X39" s="22"/>
-      <c r="Y39" s="22"/>
-      <c r="Z39" s="22"/>
-      <c r="AA39" s="22"/>
-      <c r="AB39" s="22"/>
-      <c r="AC39" s="22"/>
-      <c r="AD39" s="22"/>
-      <c r="AE39" s="22"/>
-      <c r="AF39" s="22"/>
-      <c r="AG39" s="22"/>
-      <c r="AH39" s="22"/>
-      <c r="AI39" s="22"/>
-      <c r="AJ39" s="22"/>
-      <c r="AK39" s="22"/>
-      <c r="AL39" s="22"/>
-      <c r="AM39" s="22"/>
-      <c r="AN39" s="22"/>
-      <c r="AO39" s="22"/>
-      <c r="AP39" s="22"/>
-      <c r="AQ39" s="22"/>
-      <c r="AR39" s="22"/>
-      <c r="AS39" s="22"/>
-      <c r="AT39" s="22"/>
-      <c r="AU39" s="22"/>
-      <c r="AV39" s="22"/>
-      <c r="AW39" s="22"/>
-      <c r="AX39" s="22"/>
-      <c r="AY39" s="22"/>
-      <c r="AZ39" s="22"/>
-      <c r="BA39" s="22"/>
-      <c r="BB39" s="22"/>
-      <c r="BC39" s="22"/>
-      <c r="BD39" s="22"/>
-      <c r="BE39" s="22"/>
-      <c r="BF39" s="22"/>
-      <c r="BG39" s="22"/>
-      <c r="BH39" s="22"/>
-      <c r="BI39" s="22"/>
-      <c r="BJ39" s="22"/>
-      <c r="BK39" s="22"/>
-      <c r="BL39" s="22"/>
+      <c r="I39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="J39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="K39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="L39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="M39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="N39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="O39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="P39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Q39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="R39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="S39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="T39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="U39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="V39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="W39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="X39" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Y39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="Z39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AA39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AB39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AC39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AD39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AE39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AF39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AG39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AH39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AI39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AJ39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AK39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AL39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AM39" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AN39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AO39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AP39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AQ39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AR39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AS39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AT39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AU39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AV39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AW39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AX39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AY39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AZ39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BA39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BB39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BC39" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BD39" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE39" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF39" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG39" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH39" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI39" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ39" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK39" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL39" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
     </row>
-    <row r="40" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
-      <c r="B40" s="57"/>
-      <c r="C40" s="53"/>
-      <c r="D40" s="53"/>
-      <c r="E40" s="54"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="56"/>
+      <c r="B40" s="127" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="54">
+        <v>0.1</v>
+      </c>
+      <c r="F40" s="55">
+        <v>46141</v>
+      </c>
+      <c r="G40" s="56">
+        <v>1</v>
+      </c>
       <c r="H40" s="53"/>
       <c r="I40" s="22" t="str">
-        <f t="shared" ref="I40:AN40" ca="1" si="13">IF(AND($C40="Goal",I$7&gt;=$F40,I$7&lt;=$F40+$G40-1),2,IF(AND($C40="Milestone",I$7&gt;=$F40,I$7&lt;=$F40+$G40-1),1,""))</f>
+        <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
       <c r="J40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="K40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="L40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="M40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="N40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="O40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="P40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Q40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="R40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="S40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="T40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="U40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="V40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="W40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="X40" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Y40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="Z40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AA40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AB40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AC40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AD40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AE40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AF40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AG40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AH40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AI40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AJ40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AK40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AL40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AM40" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AN40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AO40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AP40" s="22">
+        <f t="shared" ca="1" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="AQ40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AR40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AS40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AT40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AU40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AV40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AW40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AX40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AY40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AZ40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BA40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BB40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BC40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BD40" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE40" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF40" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG40" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH40" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI40" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ40" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK40" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL40" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="9"/>
+      <c r="B41" s="126" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="54">
+        <v>1</v>
+      </c>
+      <c r="F41" s="55">
+        <v>46141</v>
+      </c>
+      <c r="G41" s="56">
+        <v>1</v>
+      </c>
+      <c r="H41" s="53"/>
+      <c r="I41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="J41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="K41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="L41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="M41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="N41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="O41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="P41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Q41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="R41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="S41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="T41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="U41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="V41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="W41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="X41" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Y41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="Z41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AA41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AB41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AC41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AD41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AE41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AF41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AG41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AH41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AI41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AJ41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AK41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AL41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AM41" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AN41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AO41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AP41" s="22">
+        <f t="shared" ca="1" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="AQ41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AR41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AS41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AT41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AU41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AV41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AW41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AX41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AY41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="AZ41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BA41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
+      </c>
+      <c r="BB41" s="22" t="str">
+        <f t="shared" ref="BB41:BL41" ca="1" si="13">IF(AND($C41="Goal",BB$7&gt;=$F41,BB$7&lt;=$F41+$G41-1),2,IF(AND($C41="Milestone",BB$7&gt;=$F41,BB$7&lt;=$F41+$G41-1),1,""))</f>
+        <v/>
+      </c>
+      <c r="BC41" s="22" t="str">
         <f t="shared" ca="1" si="13"/>
         <v/>
       </c>
-      <c r="K40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="L40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="M40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="N40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="O40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="P40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="Q40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="R40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="S40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="T40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="U40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="V40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="W40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="X40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="Y40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="Z40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AA40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AB40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AC40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AD40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AE40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AF40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AG40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AH40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AI40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AJ40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AK40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AL40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AM40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AN40" s="22" t="str">
-        <f t="shared" ca="1" si="13"/>
-        <v/>
-      </c>
-      <c r="AO40" s="22" t="str">
-        <f t="shared" ref="AO40:BL40" ca="1" si="14">IF(AND($C40="Goal",AO$7&gt;=$F40,AO$7&lt;=$F40+$G40-1),2,IF(AND($C40="Milestone",AO$7&gt;=$F40,AO$7&lt;=$F40+$G40-1),1,""))</f>
-        <v/>
-      </c>
-      <c r="AP40" s="22" t="str">
+      <c r="BD41" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE41" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF41" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG41" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH41" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI41" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ41" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK41" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL41" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="9"/>
+      <c r="B42" s="126" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E42" s="54">
+        <v>1</v>
+      </c>
+      <c r="F42" s="55">
+        <v>46148</v>
+      </c>
+      <c r="G42" s="56">
+        <v>1</v>
+      </c>
+      <c r="H42" s="53"/>
+      <c r="I42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="J42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="K42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="L42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="M42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="N42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="O42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="P42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Q42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="R42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="S42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="T42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="U42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="V42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="W42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="X42" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Y42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="Z42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AA42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AB42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AC42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AD42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AE42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AF42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AG42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AH42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AI42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AJ42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AK42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AL42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AM42" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
+      </c>
+      <c r="AN42" s="22" t="str">
+        <f t="shared" ref="AN42:BC53" ca="1" si="14">IF(AND($C42="Goal",AN$7&gt;=$F42,AN$7&lt;=$F42+$G42-1),2,IF(AND($C42="Milestone",AN$7&gt;=$F42,AN$7&lt;=$F42+$G42-1),1,""))</f>
+        <v/>
+      </c>
+      <c r="AO42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="AQ40" s="22" t="str">
+      <c r="AP42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="AR40" s="22" t="str">
+      <c r="AQ42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="AS40" s="22" t="str">
+      <c r="AR42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="AT40" s="22" t="str">
+      <c r="AS42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="AU40" s="22" t="str">
+      <c r="AT42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="AV40" s="22" t="str">
+      <c r="AU42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="AW40" s="22" t="str">
+      <c r="AV42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="AX40" s="22" t="str">
+      <c r="AW42" s="22">
         <f t="shared" ca="1" si="14"/>
-        <v/>
-      </c>
-      <c r="AY40" s="22" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="AZ40" s="22" t="str">
+      <c r="AY42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BA40" s="22" t="str">
+      <c r="AZ42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BB40" s="22" t="str">
+      <c r="BA42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BC40" s="22" t="str">
+      <c r="BB42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BD40" s="22" t="str">
+      <c r="BC42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BE40" s="22" t="str">
+      <c r="BD42" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE42" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF42" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG42" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH42" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI42" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ42" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK42" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL42" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="9"/>
+      <c r="B43" s="127" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E43" s="54">
+        <v>1</v>
+      </c>
+      <c r="F43" s="55">
+        <v>46148</v>
+      </c>
+      <c r="G43" s="56">
+        <v>2</v>
+      </c>
+      <c r="H43" s="53"/>
+      <c r="I43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="J43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="K43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="L43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="M43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="N43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="O43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="P43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="Q43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="R43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="S43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="T43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="U43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="V43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="W43" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
+      </c>
+      <c r="X43" s="22" t="str">
+        <f t="shared" ref="X43:AM53" ca="1" si="15">IF(AND($C43="Goal",X$7&gt;=$F43,X$7&lt;=$F43+$G43-1),2,IF(AND($C43="Milestone",X$7&gt;=$F43,X$7&lt;=$F43+$G43-1),1,""))</f>
+        <v/>
+      </c>
+      <c r="Y43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="Z43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AA43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AB43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AC43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AD43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AE43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AF43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AG43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AH43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AI43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AJ43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AK43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AL43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AM43" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AN43" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BF40" s="22" t="str">
+      <c r="AO43" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BG40" s="22" t="str">
+      <c r="AP43" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BH40" s="22" t="str">
+      <c r="AQ43" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BI40" s="22" t="str">
+      <c r="AR43" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BJ40" s="22" t="str">
+      <c r="AS43" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BK40" s="22" t="str">
+      <c r="AT43" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BL40" s="22" t="str">
+      <c r="AU43" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BM40" s="83"/>
+      <c r="AV43" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AW43" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AX43" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AY43" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AZ43" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BA43" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BB43" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BC43" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BD43" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE43" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF43" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG43" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH43" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI43" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ43" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK43" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL43" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
     </row>
-    <row r="41" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="10"/>
-      <c r="B41" s="111" t="s">
+    <row r="44" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="9"/>
+      <c r="B44" s="127" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E44" s="54">
+        <v>1</v>
+      </c>
+      <c r="F44" s="55">
+        <v>46148</v>
+      </c>
+      <c r="G44" s="56">
+        <v>6</v>
+      </c>
+      <c r="H44" s="53"/>
+      <c r="I44" s="22" t="str">
+        <f t="shared" ref="I44:X53" ca="1" si="16">IF(AND($C44="Goal",I$7&gt;=$F44,I$7&lt;=$F44+$G44-1),2,IF(AND($C44="Milestone",I$7&gt;=$F44,I$7&lt;=$F44+$G44-1),1,""))</f>
+        <v/>
+      </c>
+      <c r="J44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="K44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="L44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="M44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="N44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="O44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="P44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Q44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="R44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="S44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="T44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="U44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="V44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="W44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="X44" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Y44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="Z44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AA44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AB44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AC44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AD44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AE44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AF44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AG44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AH44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AI44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AJ44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AK44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AL44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AM44" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AN44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AO44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AP44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AQ44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AR44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AS44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AT44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AU44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AV44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AW44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AX44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AY44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AZ44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BA44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BB44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BC44" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BD44" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE44" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF44" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG44" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH44" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI44" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ44" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK44" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL44" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="9"/>
+      <c r="B45" s="126" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" s="54">
+        <v>1</v>
+      </c>
+      <c r="F45" s="55">
+        <v>46155</v>
+      </c>
+      <c r="G45" s="56">
+        <v>1</v>
+      </c>
+      <c r="H45" s="53"/>
+      <c r="I45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="J45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="K45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="L45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="M45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="N45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="O45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="P45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Q45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="R45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="S45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="T45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="U45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="V45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="W45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="X45" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Y45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="Z45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AA45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AB45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AC45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AD45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AE45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AF45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AG45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AH45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AI45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AJ45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AK45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AL45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AM45" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AN45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AO45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AP45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AQ45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AR45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AS45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AT45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AU45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AV45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AW45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AX45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AY45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AZ45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BA45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BB45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BC45" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BD45" s="22">
+        <f t="shared" ca="1" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="BE45" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF45" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG45" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH45" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI45" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ45" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK45" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL45" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="9"/>
+      <c r="B46" s="127" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E46" s="54">
+        <v>0.2</v>
+      </c>
+      <c r="F46" s="55">
+        <v>46155</v>
+      </c>
+      <c r="G46" s="56">
+        <v>6</v>
+      </c>
+      <c r="H46" s="53"/>
+      <c r="I46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="J46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="K46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="L46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="M46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="N46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="O46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="P46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Q46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="R46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="S46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="T46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="U46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="V46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="W46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="X46" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Y46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="Z46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AA46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AB46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AC46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AD46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AE46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AF46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AG46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AH46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AI46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AJ46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AK46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AL46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AM46" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AN46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AO46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AP46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AQ46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AR46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AS46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AT46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AU46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AV46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AW46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AX46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AY46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AZ46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BA46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BB46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BC46" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BD46" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE46" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF46" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG46" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH46" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI46" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ46" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK46" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL46" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="9"/>
+      <c r="B47" s="126" t="s">
+        <v>78</v>
+      </c>
+      <c r="C47" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E47" s="54"/>
+      <c r="F47" s="55">
+        <v>46162</v>
+      </c>
+      <c r="G47" s="56">
+        <v>1</v>
+      </c>
+      <c r="H47" s="53"/>
+      <c r="I47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="J47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="K47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="L47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="M47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="N47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="O47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="P47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Q47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="R47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="S47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="T47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="U47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="V47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="W47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="X47" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Y47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="Z47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AA47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AB47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AC47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AD47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AE47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AF47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AG47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AH47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AI47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AJ47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AK47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AL47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AM47" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AN47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AO47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AP47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AQ47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AR47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AS47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AT47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AU47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AV47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AW47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AX47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AY47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AZ47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BA47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BB47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BC47" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BD47" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE47" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF47" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG47" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH47" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI47" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ47" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK47" s="22">
+        <f t="shared" ca="1" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="BL47" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="9"/>
+      <c r="B48" s="127" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E48" s="54"/>
+      <c r="F48" s="55">
+        <v>46162</v>
+      </c>
+      <c r="G48" s="56"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="J48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="K48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="L48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="M48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="N48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="O48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="P48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Q48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="R48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="S48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="T48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="U48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="V48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="W48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="X48" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Y48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="Z48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AA48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AB48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AC48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AD48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AE48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AF48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AG48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AH48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AI48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AJ48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AK48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AL48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AM48" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AN48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AO48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AP48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AQ48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AR48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AS48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AT48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AU48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AV48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AW48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AX48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AY48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AZ48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BA48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BB48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BC48" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BD48" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE48" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF48" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG48" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH48" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI48" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ48" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK48" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL48" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="9"/>
+      <c r="B49" s="127" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" s="54"/>
+      <c r="F49" s="55">
+        <v>46162</v>
+      </c>
+      <c r="G49" s="56"/>
+      <c r="H49" s="53"/>
+      <c r="I49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="J49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="K49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="L49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="M49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="N49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="O49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="P49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Q49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="R49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="S49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="T49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="U49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="V49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="W49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="X49" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Y49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="Z49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AA49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AB49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AC49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AD49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AE49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AF49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AG49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AH49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AI49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AJ49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AK49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AL49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AM49" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AN49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AO49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AP49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AQ49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AR49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AS49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AT49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AU49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AV49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AW49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AX49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AY49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AZ49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BA49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BB49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BC49" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BD49" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE49" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF49" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG49" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH49" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI49" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ49" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK49" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL49" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="9"/>
+      <c r="B50" s="127" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" s="53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E50" s="54"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="53"/>
+      <c r="I50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="J50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="K50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="L50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="M50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="N50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="O50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="P50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Q50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="R50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="S50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="T50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="U50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="V50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="W50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="X50" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Y50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="Z50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AA50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AB50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AC50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AD50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AE50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AF50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AG50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AH50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AI50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AJ50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AK50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AL50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AM50" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AN50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AO50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AP50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AQ50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AR50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AS50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AT50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AU50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AV50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AW50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AX50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AY50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AZ50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BA50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BB50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BC50" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BD50" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE50" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF50" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG50" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH50" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI50" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ50" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK50" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL50" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="9"/>
+      <c r="B51" s="127" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E51" s="54"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="J51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="K51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="L51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="M51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="N51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="O51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="P51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Q51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="R51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="S51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="T51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="U51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="V51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="W51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="X51" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Y51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="Z51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AA51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AB51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AC51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AD51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AE51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AF51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AG51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AH51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AI51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AJ51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AK51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AL51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AM51" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AN51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AO51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AP51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AQ51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AR51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AS51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AT51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AU51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AV51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AW51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AX51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AY51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AZ51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BA51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BB51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BC51" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BD51" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE51" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF51" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG51" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH51" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI51" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ51" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK51" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL51" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="9"/>
+      <c r="B52" s="127" t="s">
+        <v>82</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="E52" s="54"/>
+      <c r="F52" s="55">
+        <v>46169</v>
+      </c>
+      <c r="G52" s="56"/>
+      <c r="H52" s="53"/>
+      <c r="I52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="J52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="K52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="L52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="M52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="N52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="O52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="P52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Q52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="R52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="S52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="T52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="U52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="V52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="W52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="X52" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Y52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="Z52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AA52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AB52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AC52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AD52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AE52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AF52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AG52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AH52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AI52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AJ52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AK52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AL52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AM52" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AN52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AO52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AP52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AQ52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AR52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AS52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AT52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AU52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AV52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AW52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AX52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AY52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AZ52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BA52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BB52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BC52" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BD52" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE52" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF52" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG52" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH52" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI52" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ52" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK52" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL52" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="9"/>
+      <c r="B53" s="127"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="54"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="53"/>
+      <c r="I53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="J53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="K53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="L53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="M53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="N53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="O53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="P53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Q53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="R53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="S53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="T53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="U53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="V53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="W53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="X53" s="22" t="str">
+        <f t="shared" ca="1" si="16"/>
+        <v/>
+      </c>
+      <c r="Y53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="Z53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AA53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AB53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AC53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AD53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AE53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AF53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AG53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AH53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AI53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AJ53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AK53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AL53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AM53" s="22" t="str">
+        <f t="shared" ca="1" si="15"/>
+        <v/>
+      </c>
+      <c r="AN53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AO53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AP53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AQ53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AR53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AS53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AT53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AU53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AV53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AW53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AX53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AY53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="AZ53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BA53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BB53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BC53" s="22" t="str">
+        <f t="shared" ca="1" si="14"/>
+        <v/>
+      </c>
+      <c r="BD53" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BE53" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BF53" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BG53" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BH53" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BI53" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BJ53" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BK53" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BL53" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
+      </c>
+      <c r="BM53" s="83"/>
+    </row>
+    <row r="54" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="10"/>
+      <c r="B54" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="79"/>
-      <c r="G41" s="80"/>
-      <c r="H41" s="53"/>
-      <c r="I41" s="81"/>
-      <c r="J41" s="81"/>
-      <c r="K41" s="81"/>
-      <c r="L41" s="81"/>
-      <c r="M41" s="81"/>
-      <c r="N41" s="81"/>
-      <c r="O41" s="81"/>
-      <c r="P41" s="81"/>
-      <c r="Q41" s="81"/>
-      <c r="R41" s="81"/>
-      <c r="S41" s="81"/>
-      <c r="T41" s="81"/>
-      <c r="U41" s="81"/>
-      <c r="V41" s="81"/>
-      <c r="W41" s="81"/>
-      <c r="X41" s="81"/>
-      <c r="Y41" s="81"/>
-      <c r="Z41" s="81"/>
-      <c r="AA41" s="81"/>
-      <c r="AB41" s="81"/>
-      <c r="AC41" s="81"/>
-      <c r="AD41" s="81"/>
-      <c r="AE41" s="81"/>
-      <c r="AF41" s="81"/>
-      <c r="AG41" s="81"/>
-      <c r="AH41" s="81"/>
-      <c r="AI41" s="81"/>
-      <c r="AJ41" s="81"/>
-      <c r="AK41" s="81"/>
-      <c r="AL41" s="81"/>
-      <c r="AM41" s="81"/>
-      <c r="AN41" s="81"/>
-      <c r="AO41" s="81"/>
-      <c r="AP41" s="81"/>
-      <c r="AQ41" s="81"/>
-      <c r="AR41" s="81"/>
-      <c r="AS41" s="81"/>
-      <c r="AT41" s="81"/>
-      <c r="AU41" s="81"/>
-      <c r="AV41" s="81"/>
-      <c r="AW41" s="81"/>
-      <c r="AX41" s="81"/>
-      <c r="AY41" s="81"/>
-      <c r="AZ41" s="81"/>
-      <c r="BA41" s="81"/>
-      <c r="BB41" s="81"/>
-      <c r="BC41" s="81"/>
-      <c r="BD41" s="81"/>
-      <c r="BE41" s="81"/>
-      <c r="BF41" s="81"/>
-      <c r="BG41" s="81"/>
-      <c r="BH41" s="81"/>
-      <c r="BI41" s="81"/>
-      <c r="BJ41" s="81"/>
-      <c r="BK41" s="81"/>
-      <c r="BL41" s="81"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="79"/>
+      <c r="G54" s="80"/>
+      <c r="H54" s="53"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="81"/>
+      <c r="L54" s="81"/>
+      <c r="M54" s="81"/>
+      <c r="N54" s="81"/>
+      <c r="O54" s="81"/>
+      <c r="P54" s="81"/>
+      <c r="Q54" s="81"/>
+      <c r="R54" s="81"/>
+      <c r="S54" s="81"/>
+      <c r="T54" s="81"/>
+      <c r="U54" s="81"/>
+      <c r="V54" s="81"/>
+      <c r="W54" s="81"/>
+      <c r="X54" s="81"/>
+      <c r="Y54" s="81"/>
+      <c r="Z54" s="81"/>
+      <c r="AA54" s="81"/>
+      <c r="AB54" s="81"/>
+      <c r="AC54" s="81"/>
+      <c r="AD54" s="81"/>
+      <c r="AE54" s="81"/>
+      <c r="AF54" s="81"/>
+      <c r="AG54" s="81"/>
+      <c r="AH54" s="81"/>
+      <c r="AI54" s="81"/>
+      <c r="AJ54" s="81"/>
+      <c r="AK54" s="81"/>
+      <c r="AL54" s="81"/>
+      <c r="AM54" s="81"/>
+      <c r="AN54" s="81"/>
+      <c r="AO54" s="81"/>
+      <c r="AP54" s="81"/>
+      <c r="AQ54" s="81"/>
+      <c r="AR54" s="81"/>
+      <c r="AS54" s="81"/>
+      <c r="AT54" s="81"/>
+      <c r="AU54" s="81"/>
+      <c r="AV54" s="81"/>
+      <c r="AW54" s="81"/>
+      <c r="AX54" s="81"/>
+      <c r="AY54" s="81"/>
+      <c r="AZ54" s="81"/>
+      <c r="BA54" s="81"/>
+      <c r="BB54" s="81"/>
+      <c r="BC54" s="81"/>
+      <c r="BD54" s="81"/>
+      <c r="BE54" s="81"/>
+      <c r="BF54" s="81"/>
+      <c r="BG54" s="81"/>
+      <c r="BH54" s="81"/>
+      <c r="BI54" s="81"/>
+      <c r="BJ54" s="81"/>
+      <c r="BK54" s="81"/>
+      <c r="BL54" s="81"/>
     </row>
-    <row r="42" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D42" s="4"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="3"/>
+    <row r="55" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D55" s="4"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="3"/>
     </row>
-    <row r="43" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D43" s="5"/>
+    <row r="56" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D56" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -11965,7 +15997,7 @@
     <mergeCell ref="N4:Q4"/>
     <mergeCell ref="S4:V4"/>
   </mergeCells>
-  <conditionalFormatting sqref="E9:E13 E15 E17 E21 E25:E27 E30:E31 E40:E41">
+  <conditionalFormatting sqref="E9:E13 E15 E17 E21 E25:E27 E30:E31 E53:E54">
     <cfRule type="dataBar" priority="16">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -12105,7 +16137,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E36:E39">
+  <conditionalFormatting sqref="E36:E52">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -12129,55 +16161,55 @@
       <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:BL41">
+  <conditionalFormatting sqref="I7:BL54">
     <cfRule type="expression" dxfId="88" priority="12">
       <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I41:BL41">
-    <cfRule type="expression" dxfId="87" priority="24" stopIfTrue="1">
+  <conditionalFormatting sqref="I10:BL53">
+    <cfRule type="expression" dxfId="87" priority="110" stopIfTrue="1">
+      <formula>AND($C10="Low Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="111" stopIfTrue="1">
+      <formula>AND($C10="High Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="112" stopIfTrue="1">
+      <formula>AND($C10="On Track",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="113" stopIfTrue="1">
+      <formula>AND($C10="Med Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="114" stopIfTrue="1">
+      <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I54:BL54">
+    <cfRule type="expression" dxfId="82" priority="24" stopIfTrue="1">
       <formula>AND(#REF!="Low Risk",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="25" stopIfTrue="1">
       <formula>AND(#REF!="High Risk",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="26" stopIfTrue="1">
       <formula>AND(#REF!="On Track",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="27" stopIfTrue="1">
       <formula>AND(#REF!="Med Risk",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="28" stopIfTrue="1">
       <formula>AND(LEN(#REF!)=0,I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:BL6">
-    <cfRule type="expression" dxfId="82" priority="14">
+    <cfRule type="expression" dxfId="77" priority="14">
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I10:BL40">
-    <cfRule type="expression" dxfId="81" priority="110" stopIfTrue="1">
-      <formula>AND($C10="Low Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="80" priority="111" stopIfTrue="1">
-      <formula>AND($C10="High Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="79" priority="112" stopIfTrue="1">
-      <formula>AND($C10="On Track",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="113" stopIfTrue="1">
-      <formula>AND($C10="Med Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="77" priority="114" stopIfTrue="1">
-      <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="13">
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" promptTitle="Scrolling Increment" prompt="Changing this number will scroll the Gantt Chart view." sqref="C7" xr:uid="{36BE1844-BE6D-4781-8CC1-3726CFEF5A1B}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10 C12:C40" xr:uid="{F5FB9DE8-F94E-4751-A43E-A2038BC34E10}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10 C12:C53" xr:uid="{F5FB9DE8-F94E-4751-A43E-A2038BC34E10}">
       <formula1>"Goal,Milestone,On Track, Low Risk, Med Risk, High Risk"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="C11" xr:uid="{F40D2BC0-4DE6-4E46-B927-0ABBD58CC55D}">
@@ -12191,8 +16223,8 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="A scrollbar is in cells I8 through BL8. _x000a_To jump forward or backward in the timeline, enter a value of 0 or higher in cell C7._x000a_A value of 0 takes you to the beginning of the chart." sqref="A8" xr:uid="{20BDAE11-8D94-4CD5-9BB5-4ED61ECE0339}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row contains headers for the project schedule.  B9 through G9 contains schedule information.  Cells I9 through BL9 contain the first letter of each day of the week for the date above that heading._x000a_All project timeline charting is auto generated." sqref="A9" xr:uid="{2FF2EDD9-EF71-4F8A-AEC1-573F570081A3}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Project information starting in cell B11 through cell G11. _x000a_Enter Milestone Description, select a Category, assign someone to the task, and enter the progress, start date, and number of days for the task to start charting._x000a_" sqref="A11" xr:uid="{F0E8EBCB-B90E-4A0B-8C81-7F34870BDCA1}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row marks the end of the Gantt milestone data. DO NOT enter anything in this row. _x000a_To add more items, insert new rows above this one._x000a_" sqref="A41" xr:uid="{924AD4A5-6654-46D8-A99A-F39984BDA1A9}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This is an empty row" sqref="A40" xr:uid="{4769C95E-0C34-4BFE-AD69-266D3B34DDAE}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row marks the end of the Gantt milestone data. DO NOT enter anything in this row. _x000a_To add more items, insert new rows above this one._x000a_" sqref="A54" xr:uid="{924AD4A5-6654-46D8-A99A-F39984BDA1A9}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This is an empty row" sqref="A53" xr:uid="{4769C95E-0C34-4BFE-AD69-266D3B34DDAE}"/>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -12249,7 +16281,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E9:E13 E15 E17 E21 E25:E27 E30:E31 E40:E41</xm:sqref>
+          <xm:sqref>E9:E13 E15 E17 E21 E25:E27 E30:E31 E53:E54</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{E11DE259-0E26-4176-8A37-397989E52933}">
@@ -12399,7 +16431,26 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E36:E39</xm:sqref>
+          <xm:sqref>E36:E52</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="109" id="{36318585-8B22-4FB7-8876-1BFC78FE3731}">
+            <x14:iconSet iconSet="3Stars" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>2</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Flags" iconId="1"/>
+              <x14:cfIcon iconSet="3Signs" iconId="0"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>I10:BL53</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="23" id="{B61B6C73-D19B-48D0-9C8D-40E9A01FF0D4}">
@@ -12418,26 +16469,7 @@
               <x14:cfIcon iconSet="3Signs" iconId="0"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>I41:BL41</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="109" id="{36318585-8B22-4FB7-8876-1BFC78FE3731}">
-            <x14:iconSet iconSet="3Stars" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>2</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Flags" iconId="1"/>
-              <x14:cfIcon iconSet="3Signs" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>I10:BL40</xm:sqref>
+          <xm:sqref>I54:BL54</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -12468,27 +16500,27 @@
     <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10"/>
-      <c r="B2" s="131" t="s">
+      <c r="B2" s="132" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="133"/>
-      <c r="P2" s="133"/>
-      <c r="Q2" s="133"/>
-      <c r="R2" s="133"/>
-      <c r="S2" s="133"/>
-      <c r="T2" s="133"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="134"/>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="134"/>
+      <c r="S2" s="134"/>
+      <c r="T2" s="134"/>
       <c r="U2" s="61"/>
       <c r="V2" s="61"/>
       <c r="W2" s="61"/>
@@ -12562,36 +16594,36 @@
         <v>18</v>
       </c>
       <c r="H4" s="69"/>
-      <c r="I4" s="134" t="s">
+      <c r="I4" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="134"/>
-      <c r="N4" s="135" t="s">
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="N4" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="135"/>
-      <c r="P4" s="135"/>
-      <c r="Q4" s="135"/>
-      <c r="S4" s="136" t="s">
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="S4" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="T4" s="136"/>
-      <c r="U4" s="136"/>
-      <c r="V4" s="136"/>
-      <c r="X4" s="129" t="s">
+      <c r="T4" s="137"/>
+      <c r="U4" s="137"/>
+      <c r="V4" s="137"/>
+      <c r="X4" s="130" t="s">
         <v>28</v>
       </c>
-      <c r="Y4" s="129"/>
-      <c r="Z4" s="129"/>
-      <c r="AA4" s="129"/>
-      <c r="AC4" s="130" t="s">
+      <c r="Y4" s="130"/>
+      <c r="Z4" s="130"/>
+      <c r="AA4" s="130"/>
+      <c r="AC4" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="AD4" s="130"/>
-      <c r="AE4" s="130"/>
-      <c r="AF4" s="130"/>
+      <c r="AD4" s="131"/>
+      <c r="AE4" s="131"/>
+      <c r="AF4" s="131"/>
     </row>
     <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
@@ -19678,27 +23710,27 @@
     <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10"/>
-      <c r="B2" s="131" t="s">
+      <c r="B2" s="132" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="132"/>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="133"/>
-      <c r="P2" s="133"/>
-      <c r="Q2" s="133"/>
-      <c r="R2" s="133"/>
-      <c r="S2" s="133"/>
-      <c r="T2" s="133"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
+      <c r="H2" s="132"/>
+      <c r="I2" s="133"/>
+      <c r="J2" s="133"/>
+      <c r="K2" s="133"/>
+      <c r="L2" s="133"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="133"/>
+      <c r="O2" s="134"/>
+      <c r="P2" s="134"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="134"/>
+      <c r="S2" s="134"/>
+      <c r="T2" s="134"/>
       <c r="U2" s="61"/>
       <c r="V2" s="61"/>
       <c r="W2" s="61"/>
@@ -19772,36 +23804,36 @@
         <v>18</v>
       </c>
       <c r="H4" s="69"/>
-      <c r="I4" s="134" t="s">
+      <c r="I4" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="134"/>
-      <c r="N4" s="135" t="s">
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="N4" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="135"/>
-      <c r="P4" s="135"/>
-      <c r="Q4" s="135"/>
-      <c r="S4" s="136" t="s">
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="S4" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="T4" s="136"/>
-      <c r="U4" s="136"/>
-      <c r="V4" s="136"/>
-      <c r="X4" s="129" t="s">
+      <c r="T4" s="137"/>
+      <c r="U4" s="137"/>
+      <c r="V4" s="137"/>
+      <c r="X4" s="130" t="s">
         <v>28</v>
       </c>
-      <c r="Y4" s="129"/>
-      <c r="Z4" s="129"/>
-      <c r="AA4" s="129"/>
-      <c r="AC4" s="130" t="s">
+      <c r="Y4" s="130"/>
+      <c r="Z4" s="130"/>
+      <c r="AA4" s="130"/>
+      <c r="AC4" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="AD4" s="130"/>
-      <c r="AE4" s="130"/>
-      <c r="AF4" s="130"/>
+      <c r="AD4" s="131"/>
+      <c r="AE4" s="131"/>
+      <c r="AF4" s="131"/>
     </row>
     <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
@@ -26888,27 +30920,27 @@
     <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10"/>
-      <c r="B2" s="139" t="s">
+      <c r="B2" s="140" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="140"/>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140"/>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140"/>
-      <c r="N2" s="140"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="142"/>
-      <c r="Q2" s="142"/>
-      <c r="R2" s="142"/>
-      <c r="S2" s="142"/>
-      <c r="T2" s="142"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="142"/>
+      <c r="P2" s="143"/>
+      <c r="Q2" s="143"/>
+      <c r="R2" s="143"/>
+      <c r="S2" s="143"/>
+      <c r="T2" s="143"/>
       <c r="U2" s="20"/>
       <c r="V2" s="20"/>
       <c r="W2" s="20"/>
@@ -27035,40 +31067,40 @@
         <v>18</v>
       </c>
       <c r="H4" s="25"/>
-      <c r="I4" s="134" t="s">
+      <c r="I4" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="134"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
       <c r="M4" s="28"/>
-      <c r="N4" s="135" t="s">
+      <c r="N4" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="135"/>
-      <c r="P4" s="135"/>
-      <c r="Q4" s="135"/>
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
       <c r="R4" s="28"/>
-      <c r="S4" s="136" t="s">
+      <c r="S4" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="T4" s="136"/>
-      <c r="U4" s="136"/>
-      <c r="V4" s="136"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137"/>
+      <c r="V4" s="137"/>
       <c r="W4" s="28"/>
-      <c r="X4" s="129" t="s">
+      <c r="X4" s="130" t="s">
         <v>28</v>
       </c>
-      <c r="Y4" s="129"/>
-      <c r="Z4" s="129"/>
-      <c r="AA4" s="129"/>
+      <c r="Y4" s="130"/>
+      <c r="Z4" s="130"/>
+      <c r="AA4" s="130"/>
       <c r="AB4" s="28"/>
-      <c r="AC4" s="130" t="s">
+      <c r="AC4" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="AD4" s="130"/>
-      <c r="AE4" s="130"/>
-      <c r="AF4" s="130"/>
+      <c r="AD4" s="131"/>
+      <c r="AE4" s="131"/>
+      <c r="AF4" s="131"/>
       <c r="AG4" s="28"/>
       <c r="AH4" s="28"/>
       <c r="AI4" s="28"/>
@@ -28147,7 +32179,7 @@
       </c>
       <c r="F12" s="119">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46155</v>
       </c>
       <c r="G12" s="120">
         <v>3</v>
@@ -32807,7 +36839,7 @@
       <c r="E31" s="118"/>
       <c r="F31" s="119">
         <f ca="1">F12+15</f>
-        <v>46155</v>
+        <v>46170</v>
       </c>
       <c r="G31" s="120">
         <v>4</v>
@@ -33051,7 +37083,7 @@
       <c r="E32" s="118"/>
       <c r="F32" s="119">
         <f ca="1">F31+3</f>
-        <v>46158</v>
+        <v>46173</v>
       </c>
       <c r="G32" s="120">
         <v>14</v>
@@ -33295,7 +37327,7 @@
       <c r="E33" s="118"/>
       <c r="F33" s="119">
         <f ca="1">F32+15</f>
-        <v>46173</v>
+        <v>46188</v>
       </c>
       <c r="G33" s="120">
         <v>6</v>
@@ -34548,27 +38580,27 @@
     <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10"/>
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="144" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="144"/>
-      <c r="M2" s="144"/>
-      <c r="N2" s="144"/>
-      <c r="O2" s="145"/>
-      <c r="P2" s="145"/>
-      <c r="Q2" s="145"/>
-      <c r="R2" s="145"/>
-      <c r="S2" s="145"/>
-      <c r="T2" s="145"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="145"/>
+      <c r="K2" s="145"/>
+      <c r="L2" s="145"/>
+      <c r="M2" s="145"/>
+      <c r="N2" s="145"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="146"/>
+      <c r="R2" s="146"/>
+      <c r="S2" s="146"/>
+      <c r="T2" s="146"/>
       <c r="U2" s="91"/>
       <c r="V2" s="91"/>
       <c r="W2" s="91"/>
@@ -34642,36 +38674,36 @@
         <v>18</v>
       </c>
       <c r="H4" s="69"/>
-      <c r="I4" s="134" t="s">
+      <c r="I4" s="135" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="134"/>
-      <c r="K4" s="134"/>
-      <c r="L4" s="134"/>
-      <c r="N4" s="135" t="s">
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="N4" s="136" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="135"/>
-      <c r="P4" s="135"/>
-      <c r="Q4" s="135"/>
-      <c r="S4" s="136" t="s">
+      <c r="O4" s="136"/>
+      <c r="P4" s="136"/>
+      <c r="Q4" s="136"/>
+      <c r="S4" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="T4" s="136"/>
-      <c r="U4" s="136"/>
-      <c r="V4" s="136"/>
-      <c r="X4" s="129" t="s">
+      <c r="T4" s="137"/>
+      <c r="U4" s="137"/>
+      <c r="V4" s="137"/>
+      <c r="X4" s="130" t="s">
         <v>28</v>
       </c>
-      <c r="Y4" s="129"/>
-      <c r="Z4" s="129"/>
-      <c r="AA4" s="129"/>
-      <c r="AC4" s="130" t="s">
+      <c r="Y4" s="130"/>
+      <c r="Z4" s="130"/>
+      <c r="AA4" s="130"/>
+      <c r="AC4" s="131" t="s">
         <v>19</v>
       </c>
-      <c r="AD4" s="130"/>
-      <c r="AE4" s="130"/>
-      <c r="AF4" s="130"/>
+      <c r="AD4" s="131"/>
+      <c r="AE4" s="131"/>
+      <c r="AF4" s="131"/>
     </row>
     <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
@@ -35650,7 +39682,7 @@
       </c>
       <c r="F12" s="55">
         <f ca="1">TODAY()</f>
-        <v>46140</v>
+        <v>46155</v>
       </c>
       <c r="G12" s="56">
         <v>3</v>
@@ -37113,7 +41145,7 @@
       </c>
       <c r="F18" s="55">
         <f ca="1">F12+6</f>
-        <v>46146</v>
+        <v>46161</v>
       </c>
       <c r="G18" s="56">
         <v>13</v>
@@ -37358,7 +41390,7 @@
       </c>
       <c r="F19" s="55">
         <f ca="1">F18+2</f>
-        <v>46148</v>
+        <v>46163</v>
       </c>
       <c r="G19" s="56">
         <v>9</v>
@@ -37603,7 +41635,7 @@
       </c>
       <c r="F20" s="55">
         <f ca="1">F19+5</f>
-        <v>46153</v>
+        <v>46168</v>
       </c>
       <c r="G20" s="56">
         <v>11</v>
@@ -37846,7 +41878,7 @@
       <c r="E21" s="54"/>
       <c r="F21" s="55">
         <f ca="1">F20+2</f>
-        <v>46155</v>
+        <v>46170</v>
       </c>
       <c r="G21" s="56">
         <v>1</v>
@@ -38087,7 +42119,7 @@
       <c r="E22" s="54"/>
       <c r="F22" s="55">
         <f ca="1">F21+1</f>
-        <v>46156</v>
+        <v>46171</v>
       </c>
       <c r="G22" s="56">
         <v>24</v>
@@ -38566,7 +42598,7 @@
       <c r="E24" s="54"/>
       <c r="F24" s="55">
         <f ca="1">F12+15</f>
-        <v>46155</v>
+        <v>46170</v>
       </c>
       <c r="G24" s="56">
         <v>4</v>
@@ -38809,7 +42841,7 @@
       <c r="E25" s="54"/>
       <c r="F25" s="55">
         <f ca="1">F24+3</f>
-        <v>46158</v>
+        <v>46173</v>
       </c>
       <c r="G25" s="56">
         <v>14</v>
@@ -39052,7 +43084,7 @@
       <c r="E26" s="54"/>
       <c r="F26" s="55">
         <f ca="1">F25+15</f>
-        <v>46173</v>
+        <v>46188</v>
       </c>
       <c r="G26" s="56">
         <v>6</v>
@@ -39295,7 +43327,7 @@
       <c r="E27" s="54"/>
       <c r="F27" s="55">
         <f ca="1">F21+22</f>
-        <v>46177</v>
+        <v>46192</v>
       </c>
       <c r="G27" s="56">
         <v>3</v>
@@ -40015,7 +44047,7 @@
       <c r="E30" s="54"/>
       <c r="F30" s="55">
         <f ca="1">F27+3</f>
-        <v>46180</v>
+        <v>46195</v>
       </c>
       <c r="G30" s="56">
         <v>15</v>
@@ -40256,7 +44288,7 @@
       <c r="E31" s="54"/>
       <c r="F31" s="55">
         <f ca="1">F30+14</f>
-        <v>46194</v>
+        <v>46209</v>
       </c>
       <c r="G31" s="56">
         <v>5</v>
@@ -40499,7 +44531,7 @@
       <c r="E32" s="54"/>
       <c r="F32" s="55">
         <f ca="1">F31+42</f>
-        <v>46236</v>
+        <v>46251</v>
       </c>
       <c r="G32" s="56">
         <v>1</v>
@@ -41715,15 +45747,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="22a266b9fa9a230c5a512669d8b298c3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eddc33fff6b14141ee5c74a0d29ea6a1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -41999,6 +46022,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -42019,14 +46051,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75C87518-DD8E-42CD-8DAC-291A323E849B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42047,6 +46071,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
   <ds:schemaRefs>

--- a/Iteration 2/Agile Gantt chart .xlsx
+++ b/Iteration 2/Agile Gantt chart .xlsx
@@ -1,43 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="1079" documentId="8_{5FCFFA2A-1C94-4F30-8EBC-885A9A0A3AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD63781A-8482-45A3-BE50-53AAA5CFEE05}"/>
+  <xr:revisionPtr revIDLastSave="1109" documentId="8_{5FCFFA2A-1C94-4F30-8EBC-885A9A0A3AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{098D54BE-D47B-4664-8D41-EFEF6F84ABAC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="415" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="415" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
     <sheet name="Gantt Chart " sheetId="21" r:id="rId2"/>
-    <sheet name="Gantt Chart - without meetings" sheetId="20" r:id="rId3"/>
-    <sheet name="Light" sheetId="17" r:id="rId4"/>
-    <sheet name="Dark" sheetId="16" r:id="rId5"/>
-    <sheet name="Color" sheetId="18" r:id="rId6"/>
+    <sheet name="Light" sheetId="17" r:id="rId3"/>
+    <sheet name="Dark" sheetId="16" r:id="rId4"/>
+    <sheet name="Color" sheetId="18" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">Color!$6:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">Dark!$6:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">Color!$6:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">Dark!$6:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Gantt Chart '!$6:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Gantt Chart - without meetings'!$6:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">Light!$6:$9</definedName>
-    <definedName name="Project_Start" localSheetId="5">Color!$C$6</definedName>
-    <definedName name="Project_Start" localSheetId="4">Dark!$C$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">Light!$6:$9</definedName>
+    <definedName name="Project_Start" localSheetId="4">Color!$C$6</definedName>
+    <definedName name="Project_Start" localSheetId="3">Dark!$C$6</definedName>
     <definedName name="Project_Start" localSheetId="1">'Gantt Chart '!$C$6</definedName>
-    <definedName name="Project_Start" localSheetId="2">'Gantt Chart - without meetings'!$C$6</definedName>
-    <definedName name="Project_Start" localSheetId="3">Light!$C$6</definedName>
+    <definedName name="Project_Start" localSheetId="2">Light!$C$6</definedName>
     <definedName name="Project_Start">#REF!</definedName>
-    <definedName name="Scrolling_Increment" localSheetId="5">Color!$C$7</definedName>
-    <definedName name="Scrolling_Increment" localSheetId="4">Dark!$C$7</definedName>
+    <definedName name="Scrolling_Increment" localSheetId="4">Color!$C$7</definedName>
+    <definedName name="Scrolling_Increment" localSheetId="3">Dark!$C$7</definedName>
     <definedName name="Scrolling_Increment" localSheetId="1">'Gantt Chart '!$C$7</definedName>
-    <definedName name="Scrolling_Increment" localSheetId="2">'Gantt Chart - without meetings'!$C$7</definedName>
-    <definedName name="Scrolling_Increment" localSheetId="3">Light!$C$7</definedName>
+    <definedName name="Scrolling_Increment" localSheetId="2">Light!$C$7</definedName>
     <definedName name="Scrolling_Increment">#REF!</definedName>
-    <definedName name="Today" localSheetId="5">TODAY()</definedName>
     <definedName name="Today" localSheetId="4">TODAY()</definedName>
+    <definedName name="Today" localSheetId="3">TODAY()</definedName>
     <definedName name="Today" localSheetId="1">TODAY()</definedName>
     <definedName name="Today" localSheetId="2">TODAY()</definedName>
-    <definedName name="Today" localSheetId="3">TODAY()</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>Task 3</t>
   </si>
@@ -333,6 +328,9 @@
   </si>
   <si>
     <t>Update README file with Iteration 3 details</t>
+  </si>
+  <si>
+    <t>Complete all tasks for Iteration 3 and submit Progress Reports</t>
   </si>
 </sst>
 </file>
@@ -1378,7 +1376,7 @@
     <cellStyle name="Title" xfId="5" builtinId="15" customBuiltin="1"/>
     <cellStyle name="zHiddenText" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="140">
+  <dxfs count="118">
     <dxf>
       <font>
         <color auto="1"/>
@@ -1649,15 +1647,15 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
       <border>
         <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
+          <color theme="9" tint="-0.24994659260841701"/>
         </left>
         <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
+          <color theme="9" tint="-0.24994659260841701"/>
         </right>
         <top style="thin">
           <color theme="0"/>
@@ -1672,15 +1670,15 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
         </patternFill>
       </fill>
       <border>
         <left style="thin">
-          <color theme="9" tint="-0.24994659260841701"/>
+          <color theme="2" tint="-9.9948118533890809E-2"/>
         </left>
         <right style="thin">
-          <color theme="9" tint="-0.24994659260841701"/>
+          <color theme="2" tint="-9.9948118533890809E-2"/>
         </right>
         <top style="thin">
           <color theme="0"/>
@@ -1758,63 +1756,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
         </patternFill>
       </fill>
       <border>
@@ -1870,7 +1812,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
       <border>
@@ -1883,7 +1825,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
+          <bgColor theme="6"/>
         </patternFill>
       </fill>
       <border>
@@ -1926,7 +1868,48 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="6"/>
+          <bgColor theme="7" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
       <border>
@@ -1952,7 +1935,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
+          <bgColor theme="6"/>
         </patternFill>
       </fill>
       <border>
@@ -1960,6 +1943,21 @@
         <right/>
         <top/>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2085,7 +2083,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+          <bgColor theme="6"/>
         </patternFill>
       </fill>
       <border>
@@ -2093,8 +2091,6 @@
         <right/>
         <top/>
         <bottom/>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2110,45 +2106,6 @@
         <bottom/>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2169,130 +2126,16 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+          <bgColor theme="9"/>
         </patternFill>
       </fill>
       <border>
         <left/>
         <right/>
         <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </left>
-        <right style="thin">
-          <color theme="2" tint="-9.9948118533890809E-2"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </left>
-        <right style="thin">
-          <color theme="9" tint="-0.24994659260841701"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color theme="7" tint="-0.24994659260841701"/>
-        </left>
-        <right style="thin">
-          <color theme="7" tint="-0.24994659260841701"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color theme="6"/>
-        </left>
-        <right style="thin">
-          <color theme="6"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2313,34 +2156,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="7" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
@@ -2349,74 +2164,6 @@
         <right/>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color rgb="FFC00000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFC00000"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="0" tint="-0.34998626667073579"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3224,121 +2971,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" relativeIndent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.249977111117893"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -3509,21 +3141,21 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="Gantt Table Style" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Gantt Table Style" pivot="0" count="4" xr9:uid="{4904D139-63E4-4221-B7C9-C6C5B7A50FAF}">
-      <tableStyleElement type="wholeTable" dxfId="139"/>
-      <tableStyleElement type="headerRow" dxfId="138"/>
-      <tableStyleElement type="firstRowStripe" dxfId="137"/>
-      <tableStyleElement type="secondRowStripe" dxfId="136"/>
+      <tableStyleElement type="wholeTable" dxfId="117"/>
+      <tableStyleElement type="headerRow" dxfId="116"/>
+      <tableStyleElement type="firstRowStripe" dxfId="115"/>
+      <tableStyleElement type="secondRowStripe" dxfId="114"/>
     </tableStyle>
     <tableStyle name="ToDoList" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="135"/>
-      <tableStyleElement type="headerRow" dxfId="134"/>
-      <tableStyleElement type="totalRow" dxfId="133"/>
-      <tableStyleElement type="firstColumn" dxfId="132"/>
-      <tableStyleElement type="lastColumn" dxfId="131"/>
-      <tableStyleElement type="firstRowStripe" dxfId="130"/>
-      <tableStyleElement type="secondRowStripe" dxfId="129"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="128"/>
-      <tableStyleElement type="secondColumnStripe" dxfId="127"/>
+      <tableStyleElement type="wholeTable" dxfId="113"/>
+      <tableStyleElement type="headerRow" dxfId="112"/>
+      <tableStyleElement type="totalRow" dxfId="111"/>
+      <tableStyleElement type="firstColumn" dxfId="110"/>
+      <tableStyleElement type="lastColumn" dxfId="109"/>
+      <tableStyleElement type="firstRowStripe" dxfId="108"/>
+      <tableStyleElement type="secondRowStripe" dxfId="107"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="106"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="105"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -3629,10 +3261,6 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="39" fmlaLink="$C$7" horiz="1" max="365" page="2" val="0"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="39" fmlaLink="$C$7" horiz="1" max="365" page="2" val="0"/>
 </file>
 
@@ -3768,61 +3396,6 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="19457" name="Scroll Bar 1" descr="Scroll bar to scroll through the Ghantt project timeline." hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s19457"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-0000014C0000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln w="9525">
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a:ln>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>8</xdr:col>
-          <xdr:colOff>31750</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>57150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>63</xdr:col>
-          <xdr:colOff>228600</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>241300</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
             <xdr:cNvPr id="16385" name="Scroll Bar 1" descr="Scroll bar to scroll through the Ghantt project timeline." hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
@@ -3859,7 +3432,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -3914,7 +3487,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -3969,8 +3542,12 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9DCD786-338F-4F4D-899D-936CC39D523A}" name="Milestones435263" displayName="Milestones435263" ref="B9:G54" totalsRowShown="0" headerRowDxfId="126" dataDxfId="125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A9DCD786-338F-4F4D-899D-936CC39D523A}" name="Milestones435263" displayName="Milestones435263" ref="B9:G54" totalsRowShown="0" headerRowDxfId="104" dataDxfId="103">
   <autoFilter ref="B9:G54" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3980,12 +3557,12 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{40445EDE-9593-4FF7-8BAE-92234704569C}" name="Milestone description" dataDxfId="124"/>
-    <tableColumn id="2" xr3:uid="{68BCB8EB-CD74-458C-BC89-842312A712BF}" name="Category" dataDxfId="123"/>
-    <tableColumn id="3" xr3:uid="{E5449758-B90F-41ED-8762-83300E9616BD}" name="Assigned to" dataDxfId="122"/>
-    <tableColumn id="4" xr3:uid="{0C1E43FF-25F9-4BA6-B852-4E28BC5D9427}" name="Progress" dataDxfId="121"/>
-    <tableColumn id="5" xr3:uid="{78F71E7D-C2CE-4D9A-AD17-E5A1BEC14C24}" name="Start" dataDxfId="120" dataCellStyle="Date"/>
-    <tableColumn id="6" xr3:uid="{05DEF285-72DF-4ADA-BA39-0ED70BDDA00E}" name="Days" dataDxfId="119" dataCellStyle="Comma [0]"/>
+    <tableColumn id="1" xr3:uid="{40445EDE-9593-4FF7-8BAE-92234704569C}" name="Milestone description" dataDxfId="102"/>
+    <tableColumn id="2" xr3:uid="{68BCB8EB-CD74-458C-BC89-842312A712BF}" name="Category" dataDxfId="101"/>
+    <tableColumn id="3" xr3:uid="{E5449758-B90F-41ED-8762-83300E9616BD}" name="Assigned to" dataDxfId="100"/>
+    <tableColumn id="4" xr3:uid="{0C1E43FF-25F9-4BA6-B852-4E28BC5D9427}" name="Progress" dataDxfId="99"/>
+    <tableColumn id="5" xr3:uid="{78F71E7D-C2CE-4D9A-AD17-E5A1BEC14C24}" name="Start" dataDxfId="98" dataCellStyle="Date"/>
+    <tableColumn id="6" xr3:uid="{05DEF285-72DF-4ADA-BA39-0ED70BDDA00E}" name="Days" dataDxfId="97" dataCellStyle="Comma [0]"/>
   </tableColumns>
   <tableStyleInfo name="ToDoList" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -3997,7 +3574,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{BE3B58B4-F4CD-42FF-AF8A-57DABD72004E}" name="Milestones43526" displayName="Milestones43526" ref="B9:G36" totalsRowShown="0" headerRowDxfId="118" dataDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD82988E-1813-40AE-BDE7-9F0200A703CB}" name="Milestones4352" displayName="Milestones4352" ref="B9:G36" totalsRowShown="0" headerRowDxfId="96" dataDxfId="95">
   <autoFilter ref="B9:G36" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4007,12 +3584,12 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{672FF862-0C07-4252-9134-1252089DA775}" name="Milestone description" dataDxfId="116"/>
-    <tableColumn id="2" xr3:uid="{48A09342-46E9-4A90-B54C-3424B55EC3D1}" name="Category" dataDxfId="115"/>
-    <tableColumn id="3" xr3:uid="{B605E6EA-8F40-4F08-9A6C-D7CF67247964}" name="Assigned to" dataDxfId="114"/>
-    <tableColumn id="4" xr3:uid="{DA0732FA-EAE6-4606-B4E6-47DB2A2B9562}" name="Progress" dataDxfId="113"/>
-    <tableColumn id="5" xr3:uid="{21DD67FA-45E1-4867-8807-A05E83F9636C}" name="Start" dataDxfId="112" dataCellStyle="Date"/>
-    <tableColumn id="6" xr3:uid="{C9828D43-9B77-44CB-89EC-F1B963F6A043}" name="Days" dataDxfId="111" dataCellStyle="Comma [0]"/>
+    <tableColumn id="1" xr3:uid="{619BF8F6-D0F1-41AD-871D-FE0240C45A93}" name="Milestone description" dataDxfId="94"/>
+    <tableColumn id="2" xr3:uid="{39BD914E-FB02-4352-846C-6D59624DC0B0}" name="Category" dataDxfId="93"/>
+    <tableColumn id="3" xr3:uid="{D274194F-BCA0-44F3-84B2-217254EE241C}" name="Assigned to" dataDxfId="92"/>
+    <tableColumn id="4" xr3:uid="{8385BC6F-56EE-4363-A106-8DB0A1E4EF5A}" name="Progress" dataDxfId="91"/>
+    <tableColumn id="5" xr3:uid="{02926609-7B93-4B6F-BE96-92EC7A949E4B}" name="Start" dataDxfId="90" dataCellStyle="Date"/>
+    <tableColumn id="6" xr3:uid="{8FF9BE8E-04B7-4B39-AC27-D2E534204BC3}" name="Days" dataDxfId="89" dataCellStyle="Comma [0]"/>
   </tableColumns>
   <tableStyleInfo name="ToDoList" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -4024,34 +3601,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DD82988E-1813-40AE-BDE7-9F0200A703CB}" name="Milestones4352" displayName="Milestones4352" ref="B9:G36" totalsRowShown="0" headerRowDxfId="110" dataDxfId="109">
-  <autoFilter ref="B9:G36" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{619BF8F6-D0F1-41AD-871D-FE0240C45A93}" name="Milestone description" dataDxfId="108"/>
-    <tableColumn id="2" xr3:uid="{39BD914E-FB02-4352-846C-6D59624DC0B0}" name="Category" dataDxfId="107"/>
-    <tableColumn id="3" xr3:uid="{D274194F-BCA0-44F3-84B2-217254EE241C}" name="Assigned to" dataDxfId="106"/>
-    <tableColumn id="4" xr3:uid="{8385BC6F-56EE-4363-A106-8DB0A1E4EF5A}" name="Progress" dataDxfId="105"/>
-    <tableColumn id="5" xr3:uid="{02926609-7B93-4B6F-BE96-92EC7A949E4B}" name="Start" dataDxfId="104" dataCellStyle="Date"/>
-    <tableColumn id="6" xr3:uid="{8FF9BE8E-04B7-4B39-AC27-D2E534204BC3}" name="Days" dataDxfId="103" dataCellStyle="Comma [0]"/>
-  </tableColumns>
-  <tableStyleInfo name="ToDoList" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{504A1905-F514-4f6f-8877-14C23A59335A}">
-      <x14:table altTextSummary="Enter Project information in this table. Enter a milestone description for a phase, task, activity, etc. in column beneath Description. Select a category in the Category column. Assign the item to someone in the Assigned To column. Update progress and watch the data bars auto update in the Progress column. Enter the start date in the Start column and number of days in the number of days column. The Ghantt data in cells J9 through BM 34 will auto update. Add new rows to the table to add more tasks."/>
-    </ext>
-  </extLst>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0EDB95CA-98FE-4198-8801-690B9B480FDF}" name="Milestones435" displayName="Milestones435" ref="B9:G43" totalsRowShown="0" headerRowDxfId="102" dataDxfId="101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0EDB95CA-98FE-4198-8801-690B9B480FDF}" name="Milestones435" displayName="Milestones435" ref="B9:G43" totalsRowShown="0" headerRowDxfId="88" dataDxfId="87">
   <autoFilter ref="B9:G43" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4061,12 +3611,12 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6E47A83D-ACD7-4EB6-9B84-5195E813945E}" name="Milestone description" dataDxfId="100"/>
-    <tableColumn id="2" xr3:uid="{529EEF64-D037-4ACF-8CA4-0C10FE2D1FBB}" name="Category" dataDxfId="99"/>
-    <tableColumn id="3" xr3:uid="{711D01BA-2785-403A-9636-CCC7E2ADA584}" name="Assigned to" dataDxfId="98"/>
-    <tableColumn id="4" xr3:uid="{62B00BEF-16BE-4692-B5E2-F287F680F2C1}" name="Progress" dataDxfId="97"/>
-    <tableColumn id="5" xr3:uid="{D6D72902-F68F-4E59-A714-AFFF520C647A}" name="Start" dataDxfId="96" dataCellStyle="Date"/>
-    <tableColumn id="6" xr3:uid="{93E698DE-286F-49ED-AA20-D0C843671DE8}" name="Days" dataDxfId="95" dataCellStyle="Comma [0]"/>
+    <tableColumn id="1" xr3:uid="{6E47A83D-ACD7-4EB6-9B84-5195E813945E}" name="Milestone description" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{529EEF64-D037-4ACF-8CA4-0C10FE2D1FBB}" name="Category" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{711D01BA-2785-403A-9636-CCC7E2ADA584}" name="Assigned to" dataDxfId="84"/>
+    <tableColumn id="4" xr3:uid="{62B00BEF-16BE-4692-B5E2-F287F680F2C1}" name="Progress" dataDxfId="83"/>
+    <tableColumn id="5" xr3:uid="{D6D72902-F68F-4E59-A714-AFFF520C647A}" name="Start" dataDxfId="82" dataCellStyle="Date"/>
+    <tableColumn id="6" xr3:uid="{93E698DE-286F-49ED-AA20-D0C843671DE8}" name="Days" dataDxfId="81" dataCellStyle="Comma [0]"/>
   </tableColumns>
   <tableStyleInfo name="Gantt Table Style" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
@@ -4077,8 +3627,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{876EA49D-634E-482B-8173-880F7B761E2C}" name="Milestones43524" displayName="Milestones43524" ref="B9:G36" totalsRowShown="0" headerRowDxfId="94">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{876EA49D-634E-482B-8173-880F7B761E2C}" name="Milestones43524" displayName="Milestones43524" ref="B9:G36" totalsRowShown="0" headerRowDxfId="80">
   <autoFilter ref="B9:G36" xr:uid="{29E5A880-80D5-4B65-B5FB-8FB3913D3D27}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4088,9 +3638,9 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{0971B905-713A-4980-8BBC-DF959C2E61F9}" name="Milestone description" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{4492A0B8-068F-4002-9E8D-E1F5FED367F0}" name="Category" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{DF1A764E-7050-4528-B7F9-B6AB99372146}" name="Assigned to" dataDxfId="91"/>
+    <tableColumn id="1" xr3:uid="{0971B905-713A-4980-8BBC-DF959C2E61F9}" name="Milestone description" dataDxfId="79"/>
+    <tableColumn id="2" xr3:uid="{4492A0B8-068F-4002-9E8D-E1F5FED367F0}" name="Category" dataDxfId="78"/>
+    <tableColumn id="3" xr3:uid="{DF1A764E-7050-4528-B7F9-B6AB99372146}" name="Assigned to" dataDxfId="77"/>
     <tableColumn id="4" xr3:uid="{47C54592-75B0-4C70-BBF8-0F40483670E9}" name="Progress"/>
     <tableColumn id="5" xr3:uid="{663FB5E0-7616-4EA5-B56A-FF069E2E07D7}" name="Start" dataCellStyle="Date"/>
     <tableColumn id="6" xr3:uid="{3B766962-C06F-4E12-BE91-12AB93439874}" name="Days" dataCellStyle="Comma [0]"/>
@@ -10064,7 +9614,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E30" s="54">
         <v>1</v>
@@ -10554,7 +10104,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="81" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E32" s="54">
         <v>1</v>
@@ -12951,7 +12501,7 @@
         <v/>
       </c>
       <c r="BB41" s="22" t="str">
-        <f t="shared" ref="BB41:BL41" ca="1" si="13">IF(AND($C41="Goal",BB$7&gt;=$F41,BB$7&lt;=$F41+$G41-1),2,IF(AND($C41="Milestone",BB$7&gt;=$F41,BB$7&lt;=$F41+$G41-1),1,""))</f>
+        <f t="shared" ref="BB41:BC41" ca="1" si="13">IF(AND($C41="Goal",BB$7&gt;=$F41,BB$7&lt;=$F41+$G41-1),2,IF(AND($C41="Milestone",BB$7&gt;=$F41,BB$7&lt;=$F41+$G41-1),1,""))</f>
         <v/>
       </c>
       <c r="BC41" s="22" t="str">
@@ -13742,7 +13292,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="53" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E45" s="54">
         <v>1</v>
@@ -13991,7 +13541,7 @@
         <v>56</v>
       </c>
       <c r="E46" s="54">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="55">
         <v>46155</v>
@@ -14236,7 +13786,9 @@
       <c r="D47" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E47" s="54"/>
+      <c r="E47" s="54">
+        <v>1</v>
+      </c>
       <c r="F47" s="55">
         <v>46162</v>
       </c>
@@ -14480,11 +14032,15 @@
       <c r="D48" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E48" s="54"/>
+      <c r="E48" s="54">
+        <v>1</v>
+      </c>
       <c r="F48" s="55">
         <v>46162</v>
       </c>
-      <c r="G48" s="56"/>
+      <c r="G48" s="56">
+        <v>6</v>
+      </c>
       <c r="H48" s="53"/>
       <c r="I48" s="22" t="str">
         <f t="shared" ca="1" si="16"/>
@@ -14722,11 +14278,15 @@
       <c r="D49" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E49" s="54"/>
+      <c r="E49" s="54">
+        <v>0.7</v>
+      </c>
       <c r="F49" s="55">
         <v>46162</v>
       </c>
-      <c r="G49" s="56"/>
+      <c r="G49" s="56">
+        <v>6</v>
+      </c>
       <c r="H49" s="53"/>
       <c r="I49" s="22" t="str">
         <f t="shared" ca="1" si="16"/>
@@ -14964,9 +14524,15 @@
       <c r="D50" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E50" s="54"/>
-      <c r="F50" s="55"/>
-      <c r="G50" s="56"/>
+      <c r="E50" s="54">
+        <v>1</v>
+      </c>
+      <c r="F50" s="55">
+        <v>46162</v>
+      </c>
+      <c r="G50" s="56">
+        <v>6</v>
+      </c>
       <c r="H50" s="53"/>
       <c r="I50" s="22" t="str">
         <f t="shared" ca="1" si="16"/>
@@ -15204,9 +14770,15 @@
       <c r="D51" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E51" s="54"/>
-      <c r="F51" s="55"/>
-      <c r="G51" s="56"/>
+      <c r="E51" s="54">
+        <v>1</v>
+      </c>
+      <c r="F51" s="55">
+        <v>46162</v>
+      </c>
+      <c r="G51" s="56">
+        <v>6</v>
+      </c>
       <c r="H51" s="53"/>
       <c r="I51" s="22" t="str">
         <f t="shared" ca="1" si="16"/>
@@ -15436,7 +15008,7 @@
     <row r="52" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9"/>
       <c r="B52" s="127" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C52" s="53" t="s">
         <v>9</v>
@@ -15444,11 +15016,15 @@
       <c r="D52" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="E52" s="54"/>
+      <c r="E52" s="54">
+        <v>0.9</v>
+      </c>
       <c r="F52" s="55">
         <v>46169</v>
       </c>
-      <c r="G52" s="56"/>
+      <c r="G52" s="56">
+        <v>1</v>
+      </c>
       <c r="H52" s="53"/>
       <c r="I52" s="22" t="str">
         <f t="shared" ca="1" si="16"/>
@@ -16152,56 +15728,56 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6">
-    <cfRule type="expression" dxfId="90" priority="15">
+    <cfRule type="expression" dxfId="76" priority="15">
       <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:BL6">
-    <cfRule type="expression" dxfId="89" priority="13">
+    <cfRule type="expression" dxfId="75" priority="13">
       <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:BL54">
-    <cfRule type="expression" dxfId="88" priority="12">
+    <cfRule type="expression" dxfId="74" priority="12">
       <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I10:BL53">
-    <cfRule type="expression" dxfId="87" priority="110" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="110" stopIfTrue="1">
       <formula>AND($C10="Low Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="111" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="111" stopIfTrue="1">
       <formula>AND($C10="High Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="112" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="112" stopIfTrue="1">
       <formula>AND($C10="On Track",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="113" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="113" stopIfTrue="1">
       <formula>AND($C10="Med Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="114" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="114" stopIfTrue="1">
       <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I54:BL54">
-    <cfRule type="expression" dxfId="82" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="24" stopIfTrue="1">
       <formula>AND(#REF!="Low Risk",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="25" stopIfTrue="1">
       <formula>AND(#REF!="High Risk",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="26" stopIfTrue="1">
       <formula>AND(#REF!="On Track",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="27" stopIfTrue="1">
       <formula>AND(#REF!="Med Risk",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="28" stopIfTrue="1">
       <formula>AND(LEN(#REF!)=0,I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:BL6">
-    <cfRule type="expression" dxfId="77" priority="14">
+    <cfRule type="expression" dxfId="63" priority="14">
       <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16478,7216 +16054,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BC0D613-5B3F-4940-BD0C-94379EDBA7F5}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:BP38"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="4.7265625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="30.7265625" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.54296875" customWidth="1"/>
-    <col min="5" max="5" width="15.7265625" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.26953125" customWidth="1"/>
-    <col min="8" max="8" width="2.7265625" hidden="1" customWidth="1"/>
-    <col min="9" max="64" width="3.54296875" customWidth="1"/>
-    <col min="65" max="65" width="2.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:68" ht="25.15" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:68" ht="49.9" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10"/>
-      <c r="B2" s="132" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="132"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
-      <c r="M2" s="133"/>
-      <c r="N2" s="133"/>
-      <c r="O2" s="134"/>
-      <c r="P2" s="134"/>
-      <c r="Q2" s="134"/>
-      <c r="R2" s="134"/>
-      <c r="S2" s="134"/>
-      <c r="T2" s="134"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="61"/>
-      <c r="AH2" s="61"/>
-      <c r="AI2" s="61"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="61"/>
-      <c r="AR2" s="61"/>
-      <c r="AS2" s="61"/>
-      <c r="AT2" s="61"/>
-      <c r="AU2" s="61"/>
-      <c r="AV2" s="61"/>
-      <c r="AW2" s="61"/>
-      <c r="AX2" s="61"/>
-      <c r="AY2" s="61"/>
-      <c r="AZ2" s="61"/>
-      <c r="BA2" s="61"/>
-      <c r="BB2" s="61"/>
-      <c r="BC2" s="61"/>
-      <c r="BD2" s="61"/>
-      <c r="BE2" s="61"/>
-      <c r="BF2" s="61"/>
-      <c r="BG2" s="61"/>
-      <c r="BH2" s="61"/>
-      <c r="BI2" s="61"/>
-      <c r="BJ2" s="61"/>
-      <c r="BK2" s="61"/>
-      <c r="BL2" s="61"/>
-      <c r="BM2" s="61"/>
-    </row>
-    <row r="3" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="10"/>
-      <c r="B3" s="62"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="10"/>
-      <c r="B4" s="66" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="71" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="69"/>
-      <c r="I4" s="135" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="135"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="135"/>
-      <c r="N4" s="136" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="136"/>
-      <c r="P4" s="136"/>
-      <c r="Q4" s="136"/>
-      <c r="S4" s="137" t="s">
-        <v>27</v>
-      </c>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137"/>
-      <c r="V4" s="137"/>
-      <c r="X4" s="130" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y4" s="130"/>
-      <c r="Z4" s="130"/>
-      <c r="AA4" s="130"/>
-      <c r="AC4" s="131" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD4" s="131"/>
-      <c r="AE4" s="131"/>
-      <c r="AF4" s="131"/>
-    </row>
-    <row r="5" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="10"/>
-      <c r="B5" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-    </row>
-    <row r="6" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="10"/>
-      <c r="B6" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="74">
-        <v>46078</v>
-      </c>
-      <c r="D6" s="75"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="85" t="str">
-        <f ca="1">TEXT(I7,"mmmm")</f>
-        <v>February</v>
-      </c>
-      <c r="J6" s="85"/>
-      <c r="K6" s="85"/>
-      <c r="L6" s="85"/>
-      <c r="M6" s="85"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="85"/>
-      <c r="P6" s="85" t="str">
-        <f ca="1">IF(TEXT(P7,"mmmm")=I6,"",TEXT(P7,"mmmm"))</f>
-        <v>March</v>
-      </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85"/>
-      <c r="S6" s="85"/>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
-      <c r="V6" s="85"/>
-      <c r="W6" s="85" t="str">
-        <f ca="1">IF(OR(TEXT(W7,"mmmm")=P6,TEXT(W7,"mmmm")=I6),"",TEXT(W7,"mmmm"))</f>
-        <v/>
-      </c>
-      <c r="X6" s="85"/>
-      <c r="Y6" s="85"/>
-      <c r="Z6" s="85"/>
-      <c r="AA6" s="85"/>
-      <c r="AB6" s="85"/>
-      <c r="AC6" s="85"/>
-      <c r="AD6" s="85" t="str">
-        <f ca="1">IF(OR(TEXT(AD7,"mmmm")=W6,TEXT(AD7,"mmmm")=P6,TEXT(AD7,"mmmm")=I6),"",TEXT(AD7,"mmmm"))</f>
-        <v/>
-      </c>
-      <c r="AE6" s="85"/>
-      <c r="AF6" s="85"/>
-      <c r="AG6" s="85"/>
-      <c r="AH6" s="85"/>
-      <c r="AI6" s="85"/>
-      <c r="AJ6" s="85"/>
-      <c r="AK6" s="85" t="str">
-        <f ca="1">IF(OR(TEXT(AK7,"mmmm")=AD6,TEXT(AK7,"mmmm")=W6,TEXT(AK7,"mmmm")=P6,TEXT(AK7,"mmmm")=I6),"",TEXT(AK7,"mmmm"))</f>
-        <v/>
-      </c>
-      <c r="AL6" s="85"/>
-      <c r="AM6" s="85"/>
-      <c r="AN6" s="85"/>
-      <c r="AO6" s="85"/>
-      <c r="AP6" s="85"/>
-      <c r="AQ6" s="85"/>
-      <c r="AR6" s="85" t="str">
-        <f ca="1">IF(OR(TEXT(AR7,"mmmm")=AK6,TEXT(AR7,"mmmm")=AD6,TEXT(AR7,"mmmm")=W6,TEXT(AR7,"mmmm")=P6),"",TEXT(AR7,"mmmm"))</f>
-        <v>April</v>
-      </c>
-      <c r="AS6" s="85"/>
-      <c r="AT6" s="85"/>
-      <c r="AU6" s="85"/>
-      <c r="AV6" s="85"/>
-      <c r="AW6" s="85"/>
-      <c r="AX6" s="86"/>
-      <c r="AY6" s="86" t="str">
-        <f ca="1">IF(OR(TEXT(AY7,"mmmm")=AR6,TEXT(AY7,"mmmm")=AK6,TEXT(AY7,"mmmm")=AD6,TEXT(AY7,"mmmm")=W6),"",TEXT(AY7,"mmmm"))</f>
-        <v/>
-      </c>
-      <c r="AZ6" s="86"/>
-      <c r="BA6" s="86"/>
-      <c r="BB6" s="87"/>
-      <c r="BC6" s="84"/>
-      <c r="BD6" s="84"/>
-      <c r="BE6" s="84"/>
-      <c r="BF6" s="84" t="str">
-        <f ca="1">IF(OR(TEXT(BF7,"mmmm")=AY6,TEXT(BF7,"mmmm")=AR6,TEXT(BF7,"mmmm")=AK6,TEXT(BF7,"mmmm")=AD6),"",TEXT(BF7,"mmmm"))</f>
-        <v/>
-      </c>
-      <c r="BG6" s="84"/>
-      <c r="BH6" s="84"/>
-      <c r="BI6" s="84"/>
-      <c r="BJ6" s="84"/>
-      <c r="BK6" s="84"/>
-      <c r="BL6" s="84"/>
-    </row>
-    <row r="7" spans="1:68" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="10"/>
-      <c r="B7" s="73" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="76">
-        <v>0</v>
-      </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="92">
-        <f ca="1">IFERROR(Project_Start+Scrolling_Increment,TODAY())</f>
-        <v>46078</v>
-      </c>
-      <c r="J7" s="93">
-        <f ca="1">I7+1</f>
-        <v>46079</v>
-      </c>
-      <c r="K7" s="93">
-        <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46080</v>
-      </c>
-      <c r="L7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46081</v>
-      </c>
-      <c r="M7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46082</v>
-      </c>
-      <c r="N7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46083</v>
-      </c>
-      <c r="O7" s="94">
-        <f t="shared" ca="1" si="0"/>
-        <v>46084</v>
-      </c>
-      <c r="P7" s="93">
-        <f ca="1">O7+1</f>
-        <v>46085</v>
-      </c>
-      <c r="Q7" s="93">
-        <f ca="1">P7+1</f>
-        <v>46086</v>
-      </c>
-      <c r="R7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46087</v>
-      </c>
-      <c r="S7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46088</v>
-      </c>
-      <c r="T7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46089</v>
-      </c>
-      <c r="U7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46090</v>
-      </c>
-      <c r="V7" s="94">
-        <f t="shared" ca="1" si="0"/>
-        <v>46091</v>
-      </c>
-      <c r="W7" s="93">
-        <f ca="1">V7+1</f>
-        <v>46092</v>
-      </c>
-      <c r="X7" s="93">
-        <f ca="1">W7+1</f>
-        <v>46093</v>
-      </c>
-      <c r="Y7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46094</v>
-      </c>
-      <c r="Z7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46095</v>
-      </c>
-      <c r="AA7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46096</v>
-      </c>
-      <c r="AB7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46097</v>
-      </c>
-      <c r="AC7" s="94">
-        <f t="shared" ca="1" si="0"/>
-        <v>46098</v>
-      </c>
-      <c r="AD7" s="93">
-        <f ca="1">AC7+1</f>
-        <v>46099</v>
-      </c>
-      <c r="AE7" s="93">
-        <f ca="1">AD7+1</f>
-        <v>46100</v>
-      </c>
-      <c r="AF7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46101</v>
-      </c>
-      <c r="AG7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46102</v>
-      </c>
-      <c r="AH7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46103</v>
-      </c>
-      <c r="AI7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46104</v>
-      </c>
-      <c r="AJ7" s="94">
-        <f t="shared" ca="1" si="0"/>
-        <v>46105</v>
-      </c>
-      <c r="AK7" s="93">
-        <f ca="1">AJ7+1</f>
-        <v>46106</v>
-      </c>
-      <c r="AL7" s="93">
-        <f ca="1">AK7+1</f>
-        <v>46107</v>
-      </c>
-      <c r="AM7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46108</v>
-      </c>
-      <c r="AN7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46109</v>
-      </c>
-      <c r="AO7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46110</v>
-      </c>
-      <c r="AP7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46111</v>
-      </c>
-      <c r="AQ7" s="94">
-        <f t="shared" ca="1" si="0"/>
-        <v>46112</v>
-      </c>
-      <c r="AR7" s="93">
-        <f ca="1">AQ7+1</f>
-        <v>46113</v>
-      </c>
-      <c r="AS7" s="93">
-        <f ca="1">AR7+1</f>
-        <v>46114</v>
-      </c>
-      <c r="AT7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46115</v>
-      </c>
-      <c r="AU7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46116</v>
-      </c>
-      <c r="AV7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46117</v>
-      </c>
-      <c r="AW7" s="93">
-        <f t="shared" ca="1" si="0"/>
-        <v>46118</v>
-      </c>
-      <c r="AX7" s="94">
-        <f t="shared" ca="1" si="0"/>
-        <v>46119</v>
-      </c>
-      <c r="AY7" s="93">
-        <f ca="1">AX7+1</f>
-        <v>46120</v>
-      </c>
-      <c r="AZ7" s="93">
-        <f ca="1">AY7+1</f>
-        <v>46121</v>
-      </c>
-      <c r="BA7" s="93">
-        <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46122</v>
-      </c>
-      <c r="BB7" s="93">
-        <f t="shared" ca="1" si="1"/>
-        <v>46123</v>
-      </c>
-      <c r="BC7" s="93">
-        <f t="shared" ca="1" si="1"/>
-        <v>46124</v>
-      </c>
-      <c r="BD7" s="93">
-        <f t="shared" ca="1" si="1"/>
-        <v>46125</v>
-      </c>
-      <c r="BE7" s="94">
-        <f t="shared" ca="1" si="1"/>
-        <v>46126</v>
-      </c>
-      <c r="BF7" s="93">
-        <f ca="1">BE7+1</f>
-        <v>46127</v>
-      </c>
-      <c r="BG7" s="93">
-        <f ca="1">BF7+1</f>
-        <v>46128</v>
-      </c>
-      <c r="BH7" s="93">
-        <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46129</v>
-      </c>
-      <c r="BI7" s="93">
-        <f t="shared" ca="1" si="2"/>
-        <v>46130</v>
-      </c>
-      <c r="BJ7" s="93">
-        <f t="shared" ca="1" si="2"/>
-        <v>46131</v>
-      </c>
-      <c r="BK7" s="93">
-        <f t="shared" ca="1" si="2"/>
-        <v>46132</v>
-      </c>
-      <c r="BL7" s="94">
-        <f t="shared" ca="1" si="2"/>
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="69"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
-      <c r="N8" s="96"/>
-      <c r="O8" s="96"/>
-      <c r="P8" s="97"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="96"/>
-      <c r="S8" s="96"/>
-      <c r="T8" s="96"/>
-      <c r="U8" s="96"/>
-      <c r="V8" s="98"/>
-      <c r="W8" s="96"/>
-      <c r="X8" s="96"/>
-      <c r="Y8" s="96"/>
-      <c r="Z8" s="96"/>
-      <c r="AA8" s="96"/>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="98"/>
-      <c r="AD8" s="96"/>
-      <c r="AE8" s="96"/>
-      <c r="AF8" s="96"/>
-      <c r="AG8" s="96"/>
-      <c r="AH8" s="96"/>
-      <c r="AI8" s="96"/>
-      <c r="AJ8" s="98"/>
-      <c r="AK8" s="96"/>
-      <c r="AL8" s="96"/>
-      <c r="AM8" s="96"/>
-      <c r="AN8" s="96"/>
-      <c r="AO8" s="96"/>
-      <c r="AP8" s="96"/>
-      <c r="AQ8" s="98"/>
-      <c r="AR8" s="96"/>
-      <c r="AS8" s="96"/>
-      <c r="AT8" s="96"/>
-      <c r="AU8" s="96"/>
-      <c r="AV8" s="96"/>
-      <c r="AW8" s="96"/>
-      <c r="AX8" s="98"/>
-      <c r="AY8" s="96"/>
-      <c r="AZ8" s="96"/>
-      <c r="BA8" s="96"/>
-      <c r="BB8" s="96"/>
-      <c r="BC8" s="96"/>
-      <c r="BD8" s="96"/>
-      <c r="BE8" s="98"/>
-      <c r="BF8" s="96"/>
-      <c r="BG8" s="96"/>
-      <c r="BH8" s="96"/>
-      <c r="BI8" s="96"/>
-      <c r="BJ8" s="96"/>
-      <c r="BK8" s="96"/>
-      <c r="BL8" s="99"/>
-    </row>
-    <row r="9" spans="1:68" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="10"/>
-      <c r="B9" s="108" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="109" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="109" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="109" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="109" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="109" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="82"/>
-      <c r="I9" s="100" t="str">
-        <f t="shared" ref="I9:BL9" ca="1" si="3">LEFT(TEXT(I7,"ddd"),1)</f>
-        <v>W</v>
-      </c>
-      <c r="J9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="K9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>F</v>
-      </c>
-      <c r="L9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="M9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="N9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>M</v>
-      </c>
-      <c r="O9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="P9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>W</v>
-      </c>
-      <c r="Q9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="R9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>F</v>
-      </c>
-      <c r="S9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="T9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="U9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>M</v>
-      </c>
-      <c r="V9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="W9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>W</v>
-      </c>
-      <c r="X9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="Y9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>F</v>
-      </c>
-      <c r="Z9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="AA9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="AB9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>M</v>
-      </c>
-      <c r="AC9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="AD9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>W</v>
-      </c>
-      <c r="AE9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="AF9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>F</v>
-      </c>
-      <c r="AG9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="AH9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="AI9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>M</v>
-      </c>
-      <c r="AJ9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="AK9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>W</v>
-      </c>
-      <c r="AL9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="AM9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>F</v>
-      </c>
-      <c r="AN9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="AO9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="AP9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>M</v>
-      </c>
-      <c r="AQ9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="AR9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>W</v>
-      </c>
-      <c r="AS9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="AT9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>F</v>
-      </c>
-      <c r="AU9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="AV9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="AW9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>M</v>
-      </c>
-      <c r="AX9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="AY9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>W</v>
-      </c>
-      <c r="AZ9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="BA9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>F</v>
-      </c>
-      <c r="BB9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="BC9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="BD9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>M</v>
-      </c>
-      <c r="BE9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="BF9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>W</v>
-      </c>
-      <c r="BG9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-      <c r="BH9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>F</v>
-      </c>
-      <c r="BI9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="BJ9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>S</v>
-      </c>
-      <c r="BK9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>M</v>
-      </c>
-      <c r="BL9" s="100" t="str">
-        <f t="shared" ca="1" si="3"/>
-        <v>T</v>
-      </c>
-    </row>
-    <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="16"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="15"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="32"/>
-      <c r="R10" s="32"/>
-      <c r="S10" s="32"/>
-      <c r="T10" s="32"/>
-      <c r="U10" s="32"/>
-      <c r="V10" s="32"/>
-      <c r="W10" s="32"/>
-      <c r="X10" s="32"/>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="32"/>
-      <c r="AA10" s="32"/>
-      <c r="AB10" s="32"/>
-      <c r="AC10" s="32"/>
-      <c r="AD10" s="32"/>
-      <c r="AE10" s="32"/>
-      <c r="AF10" s="32"/>
-      <c r="AG10" s="32"/>
-      <c r="AH10" s="32"/>
-      <c r="AI10" s="32"/>
-      <c r="AJ10" s="32"/>
-      <c r="AK10" s="32"/>
-      <c r="AL10" s="32"/>
-      <c r="AM10" s="32"/>
-      <c r="AN10" s="32"/>
-      <c r="AO10" s="32"/>
-      <c r="AP10" s="32"/>
-      <c r="AQ10" s="32"/>
-      <c r="AR10" s="32"/>
-      <c r="AS10" s="32"/>
-      <c r="AT10" s="32"/>
-      <c r="AU10" s="32"/>
-      <c r="AV10" s="32"/>
-      <c r="AW10" s="32"/>
-      <c r="AX10" s="32"/>
-      <c r="AY10" s="32"/>
-      <c r="AZ10" s="32"/>
-      <c r="BA10" s="32"/>
-      <c r="BB10" s="32"/>
-      <c r="BC10" s="32"/>
-      <c r="BD10" s="32"/>
-      <c r="BE10" s="32"/>
-      <c r="BF10" s="32"/>
-      <c r="BG10" s="32"/>
-      <c r="BH10" s="32"/>
-      <c r="BI10" s="32"/>
-      <c r="BJ10" s="32"/>
-      <c r="BK10" s="32"/>
-      <c r="BL10" s="32"/>
-    </row>
-    <row r="11" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="10"/>
-      <c r="B11" s="124" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="56"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="22" t="str">
-        <f t="shared" ref="I11:X26" ca="1" si="4">IF(AND($C11="Goal",I$7&gt;=$F11,I$7&lt;=$F11+$G11-1),2,IF(AND($C11="Milestone",I$7&gt;=$F11,I$7&lt;=$F11+$G11-1),1,""))</f>
-        <v/>
-      </c>
-      <c r="J11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X11" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y11" s="22" t="str">
-        <f t="shared" ref="Y11:AN26" ca="1" si="5">IF(AND($C11="Goal",Y$7&gt;=$F11,Y$7&lt;=$F11+$G11-1),2,IF(AND($C11="Milestone",Y$7&gt;=$F11,Y$7&lt;=$F11+$G11-1),1,""))</f>
-        <v/>
-      </c>
-      <c r="Z11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN11" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO11" s="22" t="str">
-        <f t="shared" ref="AO11:BD26" ca="1" si="6">IF(AND($C11="Goal",AO$7&gt;=$F11,AO$7&lt;=$F11+$G11-1),2,IF(AND($C11="Milestone",AO$7&gt;=$F11,AO$7&lt;=$F11+$G11-1),1,""))</f>
-        <v/>
-      </c>
-      <c r="AP11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD11" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE11" s="22" t="str">
-        <f t="shared" ref="BE11:BL26" ca="1" si="7">IF(AND($C11="Goal",BE$7&gt;=$F11,BE$7&lt;=$F11+$G11-1),2,IF(AND($C11="Milestone",BE$7&gt;=$F11,BE$7&lt;=$F11+$G11-1),1,""))</f>
-        <v/>
-      </c>
-      <c r="BF11" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG11" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH11" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI11" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ11" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK11" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL11" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BP11" s="37"/>
-    </row>
-    <row r="12" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="10"/>
-      <c r="B12" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="81" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="81" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="54">
-        <v>1</v>
-      </c>
-      <c r="F12" s="55">
-        <v>46078</v>
-      </c>
-      <c r="G12" s="56">
-        <v>1</v>
-      </c>
-      <c r="H12" s="53"/>
-      <c r="I12" s="22">
-        <f ca="1">IF(AND($C12="Goal",I$7&gt;=$F12,I$7&lt;=$F12+$G12-1),2,IF(AND($C12="Milestone",I$7&gt;=$F12,I$7&lt;=$F12+$G12-1),1,""))</f>
-        <v>2</v>
-      </c>
-      <c r="J12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X12" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN12" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD12" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE12" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF12" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG12" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH12" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI12" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ12" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK12" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL12" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="10"/>
-      <c r="B13" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="81" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="54">
-        <v>1</v>
-      </c>
-      <c r="F13" s="55">
-        <v>46078</v>
-      </c>
-      <c r="G13" s="56">
-        <v>5</v>
-      </c>
-      <c r="H13" s="53"/>
-      <c r="I13" s="22" t="str">
-        <f t="shared" ref="I13:X28" ca="1" si="8">IF(AND($C13="Goal",I$7&gt;=$F13,I$7&lt;=$F13+$G13-1),2,IF(AND($C13="Milestone",I$7&gt;=$F13,I$7&lt;=$F13+$G13-1),1,""))</f>
-        <v/>
-      </c>
-      <c r="J13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X13" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN13" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD13" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE13" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF13" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG13" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH13" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI13" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ13" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK13" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL13" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9"/>
-      <c r="B14" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="81" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="54">
-        <v>1</v>
-      </c>
-      <c r="F14" s="55">
-        <v>46085</v>
-      </c>
-      <c r="G14" s="56">
-        <v>7</v>
-      </c>
-      <c r="H14" s="53"/>
-      <c r="I14" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L14" s="22" t="str">
-        <f ca="1">IF(AND($C14="Goal",L$7&gt;=$F14,L$7&lt;=$F14+$G14-1),2,IF(AND($C14="Milestone",L$7&gt;=$F14,L$7&lt;=$F14+$G14-1),1,""))</f>
-        <v/>
-      </c>
-      <c r="M14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X14" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN14" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD14" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE14" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF14" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG14" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH14" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI14" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ14" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK14" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL14" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9"/>
-      <c r="B15" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="81" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="81" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="54">
-        <v>1</v>
-      </c>
-      <c r="F15" s="55">
-        <v>46091</v>
-      </c>
-      <c r="G15" s="56">
-        <v>8</v>
-      </c>
-      <c r="H15" s="53"/>
-      <c r="I15" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X15" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN15" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD15" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE15" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF15" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG15" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH15" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI15" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ15" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK15" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL15" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:68" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="9"/>
-      <c r="B16" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="81" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="54">
-        <v>1</v>
-      </c>
-      <c r="F16" s="55">
-        <v>46091</v>
-      </c>
-      <c r="G16" s="56">
-        <v>8</v>
-      </c>
-      <c r="H16" s="53"/>
-      <c r="I16" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X16" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN16" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD16" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE16" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF16" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG16" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH16" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI16" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ16" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK16" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL16" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="10"/>
-      <c r="B17" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="81" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="54">
-        <v>1</v>
-      </c>
-      <c r="F17" s="55">
-        <v>46091</v>
-      </c>
-      <c r="G17" s="56">
-        <v>8</v>
-      </c>
-      <c r="H17" s="53"/>
-      <c r="I17" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X17" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN17" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD17" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE17" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF17" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG17" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH17" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI17" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ17" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK17" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL17" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="10"/>
-      <c r="B18" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="81" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="81" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="54">
-        <v>1</v>
-      </c>
-      <c r="F18" s="55">
-        <v>46099</v>
-      </c>
-      <c r="G18" s="56">
-        <v>1</v>
-      </c>
-      <c r="H18" s="53"/>
-      <c r="I18" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X18" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD18" s="22">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="AE18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN18" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD18" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE18" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF18" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG18" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH18" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI18" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ18" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK18" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL18" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="9"/>
-      <c r="B19" s="124" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="81"/>
-      <c r="D19" s="81"/>
-      <c r="E19" s="54"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X19" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN19" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD19" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE19" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF19" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG19" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH19" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI19" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ19" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK19" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL19" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="9"/>
-      <c r="B20" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="81" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="81" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="54">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="F20" s="55">
-        <v>46099</v>
-      </c>
-      <c r="G20" s="56">
-        <v>1</v>
-      </c>
-      <c r="H20" s="53"/>
-      <c r="I20" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X20" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD20" s="22">
-        <f t="shared" ca="1" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="AE20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN20" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD20" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE20" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF20" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG20" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH20" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI20" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ20" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK20" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL20" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="9"/>
-      <c r="B21" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="81" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="81" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="54">
-        <v>1</v>
-      </c>
-      <c r="F21" s="55">
-        <v>46106</v>
-      </c>
-      <c r="G21" s="56">
-        <v>1</v>
-      </c>
-      <c r="H21" s="53"/>
-      <c r="I21" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X21" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK21" s="22">
-        <f t="shared" ca="1" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="AL21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN21" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD21" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE21" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF21" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG21" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH21" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI21" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ21" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK21" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL21" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="9"/>
-      <c r="B22" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" s="81" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="54">
-        <v>1</v>
-      </c>
-      <c r="F22" s="55">
-        <v>46112</v>
-      </c>
-      <c r="G22" s="56">
-        <v>2</v>
-      </c>
-      <c r="H22" s="53"/>
-      <c r="I22" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X22" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN22" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD22" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE22" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF22" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG22" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH22" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI22" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ22" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK22" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL22" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="9"/>
-      <c r="B23" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="81" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="81" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="F23" s="55">
-        <v>46134</v>
-      </c>
-      <c r="G23" s="56">
-        <v>6</v>
-      </c>
-      <c r="H23" s="53"/>
-      <c r="I23" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X23" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN23" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD23" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE23" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF23" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG23" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH23" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI23" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ23" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK23" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL23" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="9"/>
-      <c r="B24" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="D24" s="81" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" s="54"/>
-      <c r="F24" s="55">
-        <v>46134</v>
-      </c>
-      <c r="G24" s="56">
-        <v>6</v>
-      </c>
-      <c r="H24" s="53"/>
-      <c r="I24" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X24" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN24" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD24" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE24" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF24" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG24" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH24" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI24" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ24" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK24" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL24" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="9"/>
-      <c r="B25" s="57" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="53" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25" s="54"/>
-      <c r="F25" s="55">
-        <v>46134</v>
-      </c>
-      <c r="G25" s="56">
-        <v>7</v>
-      </c>
-      <c r="H25" s="53"/>
-      <c r="I25" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X25" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN25" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AO25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD25" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BE25" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF25" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG25" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH25" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI25" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ25" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK25" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL25" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="26" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="9"/>
-      <c r="B26" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="53" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" s="54"/>
-      <c r="F26" s="55">
-        <v>46134</v>
-      </c>
-      <c r="G26" s="56">
-        <v>6</v>
-      </c>
-      <c r="H26" s="53"/>
-      <c r="I26" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="K26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X26" s="22" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="Z26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AA26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AB26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AC26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AD26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AE26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AF26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AG26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AH26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AI26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AJ26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AK26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AL26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AM26" s="22" t="str">
-        <f t="shared" ca="1" si="5"/>
-        <v/>
-      </c>
-      <c r="AN26" s="22" t="str">
-        <f t="shared" ref="AN26:BC35" ca="1" si="9">IF(AND($C26="Goal",AN$7&gt;=$F26,AN$7&lt;=$F26+$G26-1),2,IF(AND($C26="Milestone",AN$7&gt;=$F26,AN$7&lt;=$F26+$G26-1),1,""))</f>
-        <v/>
-      </c>
-      <c r="AO26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AP26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AQ26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AR26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AS26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AT26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AU26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AV26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AW26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AX26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AY26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="AZ26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BA26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BB26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BC26" s="22" t="str">
-        <f t="shared" ca="1" si="6"/>
-        <v/>
-      </c>
-      <c r="BD26" s="22" t="str">
-        <f t="shared" ref="BD26:BL35" ca="1" si="10">IF(AND($C26="Goal",BD$7&gt;=$F26,BD$7&lt;=$F26+$G26-1),2,IF(AND($C26="Milestone",BD$7&gt;=$F26,BD$7&lt;=$F26+$G26-1),1,""))</f>
-        <v/>
-      </c>
-      <c r="BE26" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BF26" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BG26" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BH26" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BI26" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BJ26" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BK26" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-      <c r="BL26" s="22" t="str">
-        <f t="shared" ca="1" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="27" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="9"/>
-      <c r="B27" s="57" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="54"/>
-      <c r="F27" s="55">
-        <v>46140</v>
-      </c>
-      <c r="G27" s="56">
-        <v>1</v>
-      </c>
-      <c r="H27" s="53"/>
-      <c r="I27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="K27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="L27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="M27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="N27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="O27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="P27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="Q27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="R27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="S27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="T27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="U27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="V27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="W27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="X27" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="Y27" s="22" t="str">
-        <f t="shared" ref="Y27:AM35" ca="1" si="11">IF(AND($C27="Goal",Y$7&gt;=$F27,Y$7&lt;=$F27+$G27-1),2,IF(AND($C27="Milestone",Y$7&gt;=$F27,Y$7&lt;=$F27+$G27-1),1,""))</f>
-        <v/>
-      </c>
-      <c r="Z27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AA27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AB27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AC27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AD27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AE27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AF27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AG27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AH27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AI27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AJ27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AK27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AL27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AM27" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AN27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AO27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AP27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AQ27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AR27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AS27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AT27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AU27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AV27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AW27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AX27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AY27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AZ27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BA27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BB27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BC27" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BD27" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BE27" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BF27" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BG27" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BH27" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BI27" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BJ27" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BK27" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BL27" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="9"/>
-      <c r="B28" s="57" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="54"/>
-      <c r="F28" s="55">
-        <v>46140</v>
-      </c>
-      <c r="G28" s="56">
-        <v>1</v>
-      </c>
-      <c r="H28" s="53"/>
-      <c r="I28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="J28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="K28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="L28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="M28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="N28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="O28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="P28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="Q28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="R28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="S28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="T28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="U28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="V28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="W28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="X28" s="22" t="str">
-        <f t="shared" ca="1" si="8"/>
-        <v/>
-      </c>
-      <c r="Y28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="Z28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AA28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AB28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AC28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AD28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AE28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AF28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AG28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AH28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AI28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AJ28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AK28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AL28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AM28" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AN28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AO28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AP28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AQ28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AR28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AS28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AT28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AU28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AV28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AW28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AX28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AY28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AZ28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BA28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BB28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BC28" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BD28" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BE28" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BF28" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BG28" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BH28" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BI28" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BJ28" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BK28" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BL28" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="9"/>
-      <c r="B29" s="110" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="53"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="54"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="53"/>
-      <c r="I29" s="22" t="str">
-        <f t="shared" ref="I29:X35" ca="1" si="12">IF(AND($C29="Goal",I$7&gt;=$F29,I$7&lt;=$F29+$G29-1),2,IF(AND($C29="Milestone",I$7&gt;=$F29,I$7&lt;=$F29+$G29-1),1,""))</f>
-        <v/>
-      </c>
-      <c r="J29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="K29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="L29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="M29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="N29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="O29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="P29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Q29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="R29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="S29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="T29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="U29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="V29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="W29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="X29" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Y29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="Z29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AA29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AB29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AC29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AD29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AE29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AF29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AG29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AH29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AI29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AJ29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AK29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AL29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AM29" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AN29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AO29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AP29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AQ29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AR29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AS29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AT29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AU29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AV29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AW29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AX29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AY29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AZ29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BA29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BB29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BC29" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BD29" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BE29" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BF29" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BG29" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BH29" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BI29" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BJ29" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BK29" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BL29" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="9"/>
-      <c r="B30" s="57" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="54"/>
-      <c r="F30" s="55">
-        <f>F27+3</f>
-        <v>46143</v>
-      </c>
-      <c r="G30" s="56">
-        <v>15</v>
-      </c>
-      <c r="H30" s="53"/>
-      <c r="I30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="J30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="K30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="L30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="M30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="N30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="O30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="P30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Q30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="R30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="S30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="T30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="U30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="V30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="W30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="X30" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Y30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="Z30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AA30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AB30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AC30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AD30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AE30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AF30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AG30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AH30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AI30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AJ30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AK30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AL30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AM30" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AN30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AO30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AP30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AQ30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AR30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AS30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AT30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AU30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AV30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AW30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AX30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AY30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AZ30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BA30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BB30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BC30" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BD30" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BE30" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BF30" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BG30" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BH30" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BI30" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BJ30" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BK30" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BL30" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="9"/>
-      <c r="B31" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="C31" s="53"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="54"/>
-      <c r="F31" s="55">
-        <f>F30+14</f>
-        <v>46157</v>
-      </c>
-      <c r="G31" s="56">
-        <v>5</v>
-      </c>
-      <c r="H31" s="53"/>
-      <c r="I31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="J31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="K31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="L31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="M31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="N31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="O31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="P31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Q31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="R31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="S31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="T31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="U31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="V31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="W31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="X31" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Y31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="Z31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AA31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AB31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AC31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AD31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AE31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AF31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AG31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AH31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AI31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AJ31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AK31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AL31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AM31" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AN31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AO31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AP31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AQ31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AR31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AS31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AT31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AU31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AV31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AW31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AX31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AY31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AZ31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BA31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BB31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BC31" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BD31" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BE31" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BF31" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BG31" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BH31" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BI31" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BJ31" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BK31" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BL31" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:64" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="9"/>
-      <c r="B32" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="53"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="55">
-        <f>F31+42</f>
-        <v>46199</v>
-      </c>
-      <c r="G32" s="56">
-        <v>1</v>
-      </c>
-      <c r="H32" s="53"/>
-      <c r="I32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="J32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="K32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="L32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="M32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="N32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="O32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="P32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Q32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="R32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="S32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="T32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="U32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="V32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="W32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="X32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Y32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="Z32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AA32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AB32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AC32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AD32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AE32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AF32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AG32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AH32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AI32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AJ32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AK32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AL32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AM32" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AN32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AO32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AP32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AQ32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AR32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AS32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AT32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AU32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AV32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AW32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AX32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AY32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AZ32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BA32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BB32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BC32" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BD32" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BE32" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BF32" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BG32" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BH32" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BI32" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BJ32" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BK32" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BL32" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="9"/>
-      <c r="B33" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="J33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="K33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="L33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="M33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="N33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="O33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="P33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Q33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="R33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="S33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="T33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="U33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="V33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="W33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="X33" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Y33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="Z33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AA33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AB33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AC33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AD33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AE33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AF33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AG33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AH33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AI33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AJ33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AK33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AL33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AM33" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AN33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AO33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AP33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AQ33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AR33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AS33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AT33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AU33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AV33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AW33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AX33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AY33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AZ33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BA33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BB33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BC33" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BD33" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BE33" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BF33" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BG33" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BH33" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BI33" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BJ33" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BK33" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BL33" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="9"/>
-      <c r="B34" s="57"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="54"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="J34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="K34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="L34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="M34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="N34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="O34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="P34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Q34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="R34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="S34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="T34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="U34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="V34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="W34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="X34" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Y34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="Z34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AA34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AB34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AC34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AD34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AE34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AF34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AG34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AH34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AI34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AJ34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AK34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AL34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AM34" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AN34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AO34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AP34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AQ34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AR34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AS34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AT34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AU34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AV34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AW34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AX34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AY34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AZ34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BA34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BB34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BC34" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BD34" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BE34" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BF34" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BG34" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BH34" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BI34" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BJ34" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BK34" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BL34" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="9"/>
-      <c r="B35" s="57"/>
-      <c r="C35" s="53"/>
-      <c r="D35" s="53"/>
-      <c r="E35" s="54"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="J35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="K35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="L35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="M35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="N35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="O35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="P35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Q35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="R35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="S35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="T35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="U35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="V35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="W35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="X35" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
-      </c>
-      <c r="Y35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="Z35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AA35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AB35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AC35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AD35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AE35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AF35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AG35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AH35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AI35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AJ35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AK35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AL35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AM35" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
-      </c>
-      <c r="AN35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AO35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AP35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AQ35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AR35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AS35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AT35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AU35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AV35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AW35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AX35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AY35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="AZ35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BA35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BB35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BC35" s="22" t="str">
-        <f t="shared" ca="1" si="9"/>
-        <v/>
-      </c>
-      <c r="BD35" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BE35" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BF35" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BG35" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BH35" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BI35" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BJ35" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BK35" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BL35" s="22" t="str">
-        <f t="shared" ca="1" si="10"/>
-        <v/>
-      </c>
-      <c r="BM35" s="83"/>
-    </row>
-    <row r="36" spans="1:65" s="1" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="10"/>
-      <c r="B36" s="111" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="69"/>
-      <c r="F36" s="79"/>
-      <c r="G36" s="80"/>
-      <c r="H36" s="53"/>
-      <c r="I36" s="81"/>
-      <c r="J36" s="81"/>
-      <c r="K36" s="81"/>
-      <c r="L36" s="81"/>
-      <c r="M36" s="81"/>
-      <c r="N36" s="81"/>
-      <c r="O36" s="81"/>
-      <c r="P36" s="81"/>
-      <c r="Q36" s="81"/>
-      <c r="R36" s="81"/>
-      <c r="S36" s="81"/>
-      <c r="T36" s="81"/>
-      <c r="U36" s="81"/>
-      <c r="V36" s="81"/>
-      <c r="W36" s="81"/>
-      <c r="X36" s="81"/>
-      <c r="Y36" s="81"/>
-      <c r="Z36" s="81"/>
-      <c r="AA36" s="81"/>
-      <c r="AB36" s="81"/>
-      <c r="AC36" s="81"/>
-      <c r="AD36" s="81"/>
-      <c r="AE36" s="81"/>
-      <c r="AF36" s="81"/>
-      <c r="AG36" s="81"/>
-      <c r="AH36" s="81"/>
-      <c r="AI36" s="81"/>
-      <c r="AJ36" s="81"/>
-      <c r="AK36" s="81"/>
-      <c r="AL36" s="81"/>
-      <c r="AM36" s="81"/>
-      <c r="AN36" s="81"/>
-      <c r="AO36" s="81"/>
-      <c r="AP36" s="81"/>
-      <c r="AQ36" s="81"/>
-      <c r="AR36" s="81"/>
-      <c r="AS36" s="81"/>
-      <c r="AT36" s="81"/>
-      <c r="AU36" s="81"/>
-      <c r="AV36" s="81"/>
-      <c r="AW36" s="81"/>
-      <c r="AX36" s="81"/>
-      <c r="AY36" s="81"/>
-      <c r="AZ36" s="81"/>
-      <c r="BA36" s="81"/>
-      <c r="BB36" s="81"/>
-      <c r="BC36" s="81"/>
-      <c r="BD36" s="81"/>
-      <c r="BE36" s="81"/>
-      <c r="BF36" s="81"/>
-      <c r="BG36" s="81"/>
-      <c r="BH36" s="81"/>
-      <c r="BI36" s="81"/>
-      <c r="BJ36" s="81"/>
-      <c r="BK36" s="81"/>
-      <c r="BL36" s="81"/>
-    </row>
-    <row r="37" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D37" s="4"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="1:65" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D38" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="X4:AA4"/>
-    <mergeCell ref="AC4:AF4"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="I2:N2"/>
-    <mergeCell ref="O2:T2"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="S4:V4"/>
-  </mergeCells>
-  <conditionalFormatting sqref="E9:E36">
-    <cfRule type="dataBar" priority="5">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1"/>
-        <color theme="6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7B815B52-B708-4E20-99FB-AD08D9041647}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6:AM6">
-    <cfRule type="expression" dxfId="76" priority="4">
-      <formula>I$7&lt;=EOMONTH($I$7,0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I6:BL6">
-    <cfRule type="expression" dxfId="75" priority="2">
-      <formula>AND(I$7&lt;=EOMONTH($I$7,1),I$7&gt;EOMONTH($I$7,0))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I7:BL36">
-    <cfRule type="expression" dxfId="74" priority="1">
-      <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I10:BL35">
-    <cfRule type="expression" dxfId="73" priority="7" stopIfTrue="1">
-      <formula>AND($C10="Low Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="8" stopIfTrue="1">
-      <formula>AND($C10="High Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="9" stopIfTrue="1">
-      <formula>AND($C10="On Track",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="70" priority="10" stopIfTrue="1">
-      <formula>AND($C10="Med Risk",I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="11" stopIfTrue="1">
-      <formula>AND(LEN($C10)=0,I$7&gt;=$F10,I$7&lt;=$F10+$G10-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I36:BL36">
-    <cfRule type="expression" dxfId="68" priority="13" stopIfTrue="1">
-      <formula>AND(#REF!="Low Risk",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="14" stopIfTrue="1">
-      <formula>AND(#REF!="High Risk",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="15" stopIfTrue="1">
-      <formula>AND(#REF!="On Track",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="16" stopIfTrue="1">
-      <formula>AND(#REF!="Med Risk",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="17" stopIfTrue="1">
-      <formula>AND(LEN(#REF!)=0,I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J6:BL6">
-    <cfRule type="expression" dxfId="63" priority="3">
-      <formula>AND(J$7&lt;=EOMONTH($I$7,2),J$7&gt;EOMONTH($I$7,0),J$7&gt;EOMONTH($I$7,1))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="13">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This is an empty row" sqref="A35" xr:uid="{2D31DECD-B4D5-4688-A184-946CE018A542}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row marks the end of the Gantt milestone data. DO NOT enter anything in this row. _x000a_To add more items, insert new rows above this one._x000a_" sqref="A36" xr:uid="{F667D6DB-634E-4A37-A074-9BE33300F1A1}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Project information starting in cell B11 through cell G11. _x000a_Enter Milestone Description, select a Category, assign someone to the task, and enter the progress, start date, and number of days for the task to start charting._x000a_" sqref="A11" xr:uid="{01627408-D73C-45E3-994F-AA5D250DE7F1}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="This row contains headers for the project schedule.  B9 through G9 contains schedule information.  Cells I9 through BL9 contain the first letter of each day of the week for the date above that heading._x000a_All project timeline charting is auto generated." sqref="A9" xr:uid="{53100EFE-EA7F-4C9B-860E-3F26B7AC8971}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="A scrollbar is in cells I8 through BL8. _x000a_To jump forward or backward in the timeline, enter a value of 0 or higher in cell C7._x000a_A value of 0 takes you to the beginning of the chart." sqref="A8" xr:uid="{F7FC2E91-5A1F-49DF-9E97-16C8714C253A}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Cells I9 through BL9 contain the day number of the month for the Month represented in the cell block above each date cell and are auto calculated._x000a_Do not modify these cells._x000a_" sqref="A7" xr:uid="{49C25911-0CA2-40A0-BBC9-2330FA6A869C}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="A Scrolling Increment is in cell C7. _x000a_Months for the dates in row 7 are displayed starting in cells I6 through cell BL6._x000a_Do not modify these cells. They are auto updated based on the project start date in cell F6." sqref="A6" xr:uid="{D6AB7C89-6BA1-4C64-A27E-743D859E7FCC}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter the name of the Project Lead in cell B5. Enter the Project Start date in cell C6 or allow the sample formula to find the smallest date value from the Gantt Data table.  _x000a_Project Start Date: label is in cell B6." sqref="A5" xr:uid="{B71654E8-2775-436B-88CB-9681BD575ABF}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Company Name in cell B4._x000a_A legend is in cells I4 through AC4.  The Legend label is in cell G4." sqref="A4" xr:uid="{84CD96C7-6C78-4E0A-B37E-10A09D7F11BA}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Create a Gantt Chart " prompt="Enter title of this project in cell B2. _x000a_Information about how to use this worksheet, including instructions for screen readers and the author of this workbook is in the About worksheet._x000a_Continue navigating down column A to hear further instructions." sqref="A2" xr:uid="{9751E8FB-64B5-479A-A184-8C431F7981FB}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="C11" xr:uid="{C485A1D6-0FA7-4529-B64C-4FE41AFEE78F}">
-      <formula1>"Goal,Milestone,On Track, Low Risk, Med Risk, High Risk"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10 C12:C35" xr:uid="{03D4B83A-808F-42C3-8A5C-1FEB2CEC9289}">
-      <formula1>"Goal,Milestone,On Track, Low Risk, Med Risk, High Risk"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" promptTitle="Scrolling Increment" prompt="Changing this number will scroll the Gantt Chart view." sqref="C7" xr:uid="{D659832A-2E5D-4D66-95EA-71129D7105F7}">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup scale="45" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter differentFirst="1" scaleWithDoc="0">
-    <oddFooter>Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x14">
-      <controls>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <control shapeId="19457" r:id="rId4" name="Scroll Bar 1">
-              <controlPr defaultSize="0" autoPict="0" altText="Scroll bar to scroll through the Ghantt project timeline.">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>8</xdr:col>
-                    <xdr:colOff>31750</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>57150</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>63</xdr:col>
-                    <xdr:colOff>228600</xdr:colOff>
-                    <xdr:row>7</xdr:row>
-                    <xdr:rowOff>241300</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-      </controls>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <tableParts count="1">
-    <tablePart r:id="rId5"/>
-  </tableParts>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7B815B52-B708-4E20-99FB-AD08D9041647}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>E9:E36</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="6" id="{14C891AA-4233-4C15-8783-13A1680A0E47}">
-            <x14:iconSet iconSet="3Stars" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>2</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Flags" iconId="1"/>
-              <x14:cfIcon iconSet="3Signs" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>I10:BL35</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{299F7049-A4CF-4698-97A1-A8FB66FFCEFE}">
-            <x14:iconSet iconSet="3Stars" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>2</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
-              <x14:cfIcon iconSet="3Flags" iconId="1"/>
-              <x14:cfIcon iconSet="3Signs" iconId="0"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>I36:BL36</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9BEAD0-786A-4F3A-BCD3-DA7444CB9941}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -30897,7 +23263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537EAE25-AFCC-4679-A578-F5918B332482}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
@@ -32179,7 +24545,7 @@
       </c>
       <c r="F12" s="119">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46168</v>
       </c>
       <c r="G12" s="120">
         <v>3</v>
@@ -36839,7 +29205,7 @@
       <c r="E31" s="118"/>
       <c r="F31" s="119">
         <f ca="1">F12+15</f>
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="G31" s="120">
         <v>4</v>
@@ -37083,7 +29449,7 @@
       <c r="E32" s="118"/>
       <c r="F32" s="119">
         <f ca="1">F31+3</f>
-        <v>46173</v>
+        <v>46186</v>
       </c>
       <c r="G32" s="120">
         <v>14</v>
@@ -37327,7 +29693,7 @@
       <c r="E33" s="118"/>
       <c r="F33" s="119">
         <f ca="1">F32+15</f>
-        <v>46188</v>
+        <v>46201</v>
       </c>
       <c r="G33" s="120">
         <v>6</v>
@@ -38235,23 +30601,23 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:AE11">
-    <cfRule type="expression" dxfId="48" priority="93">
-      <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
+    <cfRule type="expression" dxfId="48" priority="103" stopIfTrue="1">
+      <formula>AND($C11="High Risk",I$7&gt;=$F11,I$7&lt;=$F11+$G11-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="106" stopIfTrue="1">
+      <formula>AND(LEN($C11)=0,I$7&gt;=$F11,I$7&lt;=$F11+$G11-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="102" stopIfTrue="1">
       <formula>AND($C11="Low Risk",I$7&gt;=$F11,I$7&lt;=$F11+$G11-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="103" stopIfTrue="1">
-      <formula>AND($C11="High Risk",I$7&gt;=$F11,I$7&lt;=$F11+$G11-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="104" stopIfTrue="1">
-      <formula>AND($C11="On Track",I$7&gt;=$F11,I$7&lt;=$F11+$G11-1)</formula>
+    <cfRule type="expression" dxfId="45" priority="93">
+      <formula>AND(TODAY()&gt;=I$7,TODAY()&lt;J$7)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="44" priority="105" stopIfTrue="1">
       <formula>AND($C11="Med Risk",I$7&gt;=$F11,I$7&lt;=$F11+$G11-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="106" stopIfTrue="1">
-      <formula>AND(LEN($C11)=0,I$7&gt;=$F11,I$7&lt;=$F11+$G11-1)</formula>
+    <cfRule type="expression" dxfId="43" priority="104" stopIfTrue="1">
+      <formula>AND($C11="On Track",I$7&gt;=$F11,I$7&lt;=$F11+$G11-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6:AM6">
@@ -38287,20 +30653,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I16:BL16">
-    <cfRule type="expression" dxfId="34" priority="27" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="31" stopIfTrue="1">
+      <formula>AND(LEN($C17)=0,I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="29" stopIfTrue="1">
+      <formula>AND($C17="On Track",I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="28" stopIfTrue="1">
+      <formula>AND($C17="High Risk",I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="27" stopIfTrue="1">
       <formula>AND($C17="Low Risk",I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="28" stopIfTrue="1">
-      <formula>AND($C17="High Risk",I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="29" stopIfTrue="1">
-      <formula>AND($C17="On Track",I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
       <formula>AND($C17="Med Risk",I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="31" stopIfTrue="1">
-      <formula>AND(LEN($C17)=0,I$7&gt;=$F17,I$7&lt;=$F17+$G17-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I17:BL17">
@@ -38310,31 +30676,31 @@
     <cfRule type="expression" dxfId="28" priority="50" stopIfTrue="1">
       <formula>AND($C20="High Risk",I$7&gt;=$F20,I$7&lt;=$F20+$G20-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="51" stopIfTrue="1">
-      <formula>AND($C20="On Track",I$7&gt;=$F20,I$7&lt;=$F20+$G20-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="52" stopIfTrue="1">
       <formula>AND($C20="Med Risk",I$7&gt;=$F20,I$7&lt;=$F20+$G20-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="53" stopIfTrue="1">
       <formula>AND(LEN($C20)=0,I$7&gt;=$F20,I$7&lt;=$F20+$G20-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="51" stopIfTrue="1">
+      <formula>AND($C20="On Track",I$7&gt;=$F20,I$7&lt;=$F20+$G20-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:BL35">
     <cfRule type="expression" dxfId="24" priority="87" stopIfTrue="1">
       <formula>AND($C25="Low Risk",I$7&gt;=$F25,I$7&lt;=$F25+$G25-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="88" stopIfTrue="1">
-      <formula>AND($C25="High Risk",I$7&gt;=$F25,I$7&lt;=$F25+$G25-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="23" priority="89" stopIfTrue="1">
       <formula>AND($C25="On Track",I$7&gt;=$F25,I$7&lt;=$F25+$G25-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="22" priority="90" stopIfTrue="1">
       <formula>AND($C25="Med Risk",I$7&gt;=$F25,I$7&lt;=$F25+$G25-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="21" priority="91" stopIfTrue="1">
       <formula>AND(LEN($C25)=0,I$7&gt;=$F25,I$7&lt;=$F25+$G25-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="88" stopIfTrue="1">
+      <formula>AND($C25="High Risk",I$7&gt;=$F25,I$7&lt;=$F25+$G25-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I36:BL36">
@@ -38347,11 +30713,11 @@
     <cfRule type="expression" dxfId="17" priority="15" stopIfTrue="1">
       <formula>AND(#REF!="On Track",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="16" stopIfTrue="1">
+    <cfRule type="expression" dxfId="16" priority="17" stopIfTrue="1">
+      <formula>AND(LEN(#REF!)=0,I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="16" stopIfTrue="1">
       <formula>AND(#REF!="Med Risk",I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="17" stopIfTrue="1">
-      <formula>AND(LEN(#REF!)=0,I$7&gt;=#REF!,I$7&lt;=#REF!+#REF!-1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:BL6">
@@ -38557,7 +30923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0BB8625-911A-4DD3-B0BE-8E3C7AEA3578}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -39682,7 +32048,7 @@
       </c>
       <c r="F12" s="55">
         <f ca="1">TODAY()</f>
-        <v>46155</v>
+        <v>46168</v>
       </c>
       <c r="G12" s="56">
         <v>3</v>
@@ -41145,7 +33511,7 @@
       </c>
       <c r="F18" s="55">
         <f ca="1">F12+6</f>
-        <v>46161</v>
+        <v>46174</v>
       </c>
       <c r="G18" s="56">
         <v>13</v>
@@ -41390,7 +33756,7 @@
       </c>
       <c r="F19" s="55">
         <f ca="1">F18+2</f>
-        <v>46163</v>
+        <v>46176</v>
       </c>
       <c r="G19" s="56">
         <v>9</v>
@@ -41635,7 +34001,7 @@
       </c>
       <c r="F20" s="55">
         <f ca="1">F19+5</f>
-        <v>46168</v>
+        <v>46181</v>
       </c>
       <c r="G20" s="56">
         <v>11</v>
@@ -41878,7 +34244,7 @@
       <c r="E21" s="54"/>
       <c r="F21" s="55">
         <f ca="1">F20+2</f>
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="G21" s="56">
         <v>1</v>
@@ -42119,7 +34485,7 @@
       <c r="E22" s="54"/>
       <c r="F22" s="55">
         <f ca="1">F21+1</f>
-        <v>46171</v>
+        <v>46184</v>
       </c>
       <c r="G22" s="56">
         <v>24</v>
@@ -42598,7 +34964,7 @@
       <c r="E24" s="54"/>
       <c r="F24" s="55">
         <f ca="1">F12+15</f>
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="G24" s="56">
         <v>4</v>
@@ -42841,7 +35207,7 @@
       <c r="E25" s="54"/>
       <c r="F25" s="55">
         <f ca="1">F24+3</f>
-        <v>46173</v>
+        <v>46186</v>
       </c>
       <c r="G25" s="56">
         <v>14</v>
@@ -43084,7 +35450,7 @@
       <c r="E26" s="54"/>
       <c r="F26" s="55">
         <f ca="1">F25+15</f>
-        <v>46188</v>
+        <v>46201</v>
       </c>
       <c r="G26" s="56">
         <v>6</v>
@@ -43327,7 +35693,7 @@
       <c r="E27" s="54"/>
       <c r="F27" s="55">
         <f ca="1">F21+22</f>
-        <v>46192</v>
+        <v>46205</v>
       </c>
       <c r="G27" s="56">
         <v>3</v>
@@ -44047,7 +36413,7 @@
       <c r="E30" s="54"/>
       <c r="F30" s="55">
         <f ca="1">F27+3</f>
-        <v>46195</v>
+        <v>46208</v>
       </c>
       <c r="G30" s="56">
         <v>15</v>
@@ -44288,7 +36654,7 @@
       <c r="E31" s="54"/>
       <c r="F31" s="55">
         <f ca="1">F30+14</f>
-        <v>46209</v>
+        <v>46222</v>
       </c>
       <c r="G31" s="56">
         <v>5</v>
@@ -44531,7 +36897,7 @@
       <c r="E32" s="54"/>
       <c r="F32" s="55">
         <f ca="1">F31+42</f>
-        <v>46251</v>
+        <v>46264</v>
       </c>
       <c r="G32" s="56">
         <v>1</v>
@@ -45747,6 +38113,34 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="22a266b9fa9a230c5a512669d8b298c3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eddc33fff6b14141ee5c74a0d29ea6a1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -46022,35 +38416,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75C87518-DD8E-42CD-8DAC-291A323E849B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -46069,24 +38455,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Iteration 2/Agile Gantt chart .xlsx
+++ b/Iteration 2/Agile Gantt chart .xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="1109" documentId="8_{5FCFFA2A-1C94-4F30-8EBC-885A9A0A3AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{098D54BE-D47B-4664-8D41-EFEF6F84ABAC}"/>
+  <xr:revisionPtr revIDLastSave="1118" documentId="8_{5FCFFA2A-1C94-4F30-8EBC-885A9A0A3AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B499FC7-3200-493C-8FC7-CF3AB52AE4DB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" tabRatio="415" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3249,7 +3249,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="39" fmlaLink="$C$7" horiz="1" max="365" page="2" val="30"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="39" fmlaLink="$C$7" horiz="1" max="365" page="2" val="50"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3402,7 +3402,7 @@
                   <a14:compatExt spid="_x0000_s16385"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000001400000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000001400000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3457,7 +3457,7 @@
                   <a14:compatExt spid="_x0000_s13313"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000001340000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000001340000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3512,7 +3512,7 @@
                   <a14:compatExt spid="_x0000_s17409"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000001440000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000001440000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4257,7 +4257,7 @@
       <c r="H6" s="69"/>
       <c r="I6" s="85" t="str">
         <f ca="1">TEXT(I7,"mmmm")</f>
-        <v>March</v>
+        <v>April</v>
       </c>
       <c r="J6" s="85"/>
       <c r="K6" s="85"/>
@@ -4267,7 +4267,7 @@
       <c r="O6" s="85"/>
       <c r="P6" s="85" t="str">
         <f ca="1">IF(TEXT(P7,"mmmm")=I6,"",TEXT(P7,"mmmm"))</f>
-        <v>April</v>
+        <v/>
       </c>
       <c r="Q6" s="85"/>
       <c r="R6" s="85"/>
@@ -4287,7 +4287,7 @@
       <c r="AC6" s="85"/>
       <c r="AD6" s="85" t="str">
         <f ca="1">IF(OR(TEXT(AD7,"mmmm")=W6,TEXT(AD7,"mmmm")=P6,TEXT(AD7,"mmmm")=I6),"",TEXT(AD7,"mmmm"))</f>
-        <v/>
+        <v>May</v>
       </c>
       <c r="AE6" s="85"/>
       <c r="AF6" s="85"/>
@@ -4307,7 +4307,7 @@
       <c r="AQ6" s="85"/>
       <c r="AR6" s="85" t="str">
         <f ca="1">IF(OR(TEXT(AR7,"mmmm")=AK6,TEXT(AR7,"mmmm")=AD6,TEXT(AR7,"mmmm")=W6,TEXT(AR7,"mmmm")=P6),"",TEXT(AR7,"mmmm"))</f>
-        <v>May</v>
+        <v/>
       </c>
       <c r="AS6" s="85"/>
       <c r="AT6" s="85"/>
@@ -4327,7 +4327,7 @@
       <c r="BE6" s="84"/>
       <c r="BF6" s="84" t="str">
         <f ca="1">IF(OR(TEXT(BF7,"mmmm")=AY6,TEXT(BF7,"mmmm")=AR6,TEXT(BF7,"mmmm")=AK6,TEXT(BF7,"mmmm")=AD6),"",TEXT(BF7,"mmmm"))</f>
-        <v/>
+        <v>June</v>
       </c>
       <c r="BG6" s="84"/>
       <c r="BH6" s="84"/>
@@ -4342,7 +4342,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="76">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D7" s="68"/>
       <c r="E7" s="69"/>
@@ -4351,227 +4351,227 @@
       <c r="H7" s="77"/>
       <c r="I7" s="92">
         <f ca="1">IFERROR(Project_Start+Scrolling_Increment,TODAY())</f>
-        <v>46108</v>
+        <v>46128</v>
       </c>
       <c r="J7" s="93">
         <f ca="1">I7+1</f>
-        <v>46109</v>
+        <v>46129</v>
       </c>
       <c r="K7" s="93">
         <f t="shared" ref="K7:AX7" ca="1" si="0">J7+1</f>
-        <v>46110</v>
+        <v>46130</v>
       </c>
       <c r="L7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46111</v>
+        <v>46131</v>
       </c>
       <c r="M7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46112</v>
+        <v>46132</v>
       </c>
       <c r="N7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46113</v>
+        <v>46133</v>
       </c>
       <c r="O7" s="94">
         <f t="shared" ca="1" si="0"/>
-        <v>46114</v>
+        <v>46134</v>
       </c>
       <c r="P7" s="93">
         <f ca="1">O7+1</f>
-        <v>46115</v>
+        <v>46135</v>
       </c>
       <c r="Q7" s="93">
         <f ca="1">P7+1</f>
-        <v>46116</v>
+        <v>46136</v>
       </c>
       <c r="R7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46117</v>
+        <v>46137</v>
       </c>
       <c r="S7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46118</v>
+        <v>46138</v>
       </c>
       <c r="T7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46119</v>
+        <v>46139</v>
       </c>
       <c r="U7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46120</v>
+        <v>46140</v>
       </c>
       <c r="V7" s="94">
         <f t="shared" ca="1" si="0"/>
-        <v>46121</v>
+        <v>46141</v>
       </c>
       <c r="W7" s="93">
         <f ca="1">V7+1</f>
-        <v>46122</v>
+        <v>46142</v>
       </c>
       <c r="X7" s="93">
         <f ca="1">W7+1</f>
-        <v>46123</v>
+        <v>46143</v>
       </c>
       <c r="Y7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46124</v>
+        <v>46144</v>
       </c>
       <c r="Z7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46125</v>
+        <v>46145</v>
       </c>
       <c r="AA7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46126</v>
+        <v>46146</v>
       </c>
       <c r="AB7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46127</v>
+        <v>46147</v>
       </c>
       <c r="AC7" s="94">
         <f t="shared" ca="1" si="0"/>
-        <v>46128</v>
+        <v>46148</v>
       </c>
       <c r="AD7" s="93">
         <f ca="1">AC7+1</f>
-        <v>46129</v>
+        <v>46149</v>
       </c>
       <c r="AE7" s="93">
         <f ca="1">AD7+1</f>
-        <v>46130</v>
+        <v>46150</v>
       </c>
       <c r="AF7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46131</v>
+        <v>46151</v>
       </c>
       <c r="AG7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46132</v>
+        <v>46152</v>
       </c>
       <c r="AH7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46133</v>
+        <v>46153</v>
       </c>
       <c r="AI7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46134</v>
+        <v>46154</v>
       </c>
       <c r="AJ7" s="94">
         <f t="shared" ca="1" si="0"/>
-        <v>46135</v>
+        <v>46155</v>
       </c>
       <c r="AK7" s="93">
         <f ca="1">AJ7+1</f>
-        <v>46136</v>
+        <v>46156</v>
       </c>
       <c r="AL7" s="93">
         <f ca="1">AK7+1</f>
-        <v>46137</v>
+        <v>46157</v>
       </c>
       <c r="AM7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46138</v>
+        <v>46158</v>
       </c>
       <c r="AN7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46139</v>
+        <v>46159</v>
       </c>
       <c r="AO7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46140</v>
+        <v>46160</v>
       </c>
       <c r="AP7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46141</v>
+        <v>46161</v>
       </c>
       <c r="AQ7" s="94">
         <f t="shared" ca="1" si="0"/>
-        <v>46142</v>
+        <v>46162</v>
       </c>
       <c r="AR7" s="93">
         <f ca="1">AQ7+1</f>
-        <v>46143</v>
+        <v>46163</v>
       </c>
       <c r="AS7" s="93">
         <f ca="1">AR7+1</f>
-        <v>46144</v>
+        <v>46164</v>
       </c>
       <c r="AT7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46145</v>
+        <v>46165</v>
       </c>
       <c r="AU7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46146</v>
+        <v>46166</v>
       </c>
       <c r="AV7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46147</v>
+        <v>46167</v>
       </c>
       <c r="AW7" s="93">
         <f t="shared" ca="1" si="0"/>
-        <v>46148</v>
+        <v>46168</v>
       </c>
       <c r="AX7" s="94">
         <f t="shared" ca="1" si="0"/>
-        <v>46149</v>
+        <v>46169</v>
       </c>
       <c r="AY7" s="93">
         <f ca="1">AX7+1</f>
-        <v>46150</v>
+        <v>46170</v>
       </c>
       <c r="AZ7" s="93">
         <f ca="1">AY7+1</f>
-        <v>46151</v>
+        <v>46171</v>
       </c>
       <c r="BA7" s="93">
         <f t="shared" ref="BA7:BE7" ca="1" si="1">AZ7+1</f>
-        <v>46152</v>
+        <v>46172</v>
       </c>
       <c r="BB7" s="93">
         <f t="shared" ca="1" si="1"/>
-        <v>46153</v>
+        <v>46173</v>
       </c>
       <c r="BC7" s="93">
         <f t="shared" ca="1" si="1"/>
-        <v>46154</v>
+        <v>46174</v>
       </c>
       <c r="BD7" s="93">
         <f t="shared" ca="1" si="1"/>
-        <v>46155</v>
+        <v>46175</v>
       </c>
       <c r="BE7" s="94">
         <f t="shared" ca="1" si="1"/>
-        <v>46156</v>
+        <v>46176</v>
       </c>
       <c r="BF7" s="93">
         <f ca="1">BE7+1</f>
-        <v>46157</v>
+        <v>46177</v>
       </c>
       <c r="BG7" s="93">
         <f ca="1">BF7+1</f>
-        <v>46158</v>
+        <v>46178</v>
       </c>
       <c r="BH7" s="93">
         <f t="shared" ref="BH7:BL7" ca="1" si="2">BG7+1</f>
-        <v>46159</v>
+        <v>46179</v>
       </c>
       <c r="BI7" s="93">
         <f t="shared" ca="1" si="2"/>
-        <v>46160</v>
+        <v>46180</v>
       </c>
       <c r="BJ7" s="93">
         <f t="shared" ca="1" si="2"/>
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="BK7" s="93">
         <f t="shared" ca="1" si="2"/>
-        <v>46162</v>
+        <v>46182</v>
       </c>
       <c r="BL7" s="94">
         <f t="shared" ca="1" si="2"/>
-        <v>46163</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="8" spans="1:68" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.35">
@@ -4663,11 +4663,11 @@
       <c r="H9" s="82"/>
       <c r="I9" s="100" t="str">
         <f t="shared" ref="I9:BL9" ca="1" si="3">LEFT(TEXT(I7,"ddd"),1)</f>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="J9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>F</v>
       </c>
       <c r="K9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -4675,27 +4675,27 @@
       </c>
       <c r="L9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="M9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>M</v>
       </c>
       <c r="N9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="O9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="P9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="Q9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>F</v>
       </c>
       <c r="R9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -4703,27 +4703,27 @@
       </c>
       <c r="S9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="T9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>M</v>
       </c>
       <c r="U9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="V9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="W9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="X9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>F</v>
       </c>
       <c r="Y9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -4731,27 +4731,27 @@
       </c>
       <c r="Z9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AA9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>M</v>
       </c>
       <c r="AB9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AC9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AD9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="AE9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>F</v>
       </c>
       <c r="AF9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -4759,27 +4759,27 @@
       </c>
       <c r="AG9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AH9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>M</v>
       </c>
       <c r="AI9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AJ9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AK9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="AL9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>F</v>
       </c>
       <c r="AM9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -4787,27 +4787,27 @@
       </c>
       <c r="AN9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AO9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>M</v>
       </c>
       <c r="AP9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AQ9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AR9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="AS9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>F</v>
       </c>
       <c r="AT9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -4815,27 +4815,27 @@
       </c>
       <c r="AU9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AV9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>M</v>
       </c>
       <c r="AW9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="AX9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="AY9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="AZ9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>F</v>
       </c>
       <c r="BA9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -4843,27 +4843,27 @@
       </c>
       <c r="BB9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="BC9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>M</v>
       </c>
       <c r="BD9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="BE9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
       <c r="BF9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>F</v>
+        <v>T</v>
       </c>
       <c r="BG9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>S</v>
+        <v>F</v>
       </c>
       <c r="BH9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -4871,19 +4871,19 @@
       </c>
       <c r="BI9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="BJ9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>M</v>
       </c>
       <c r="BK9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>W</v>
+        <v>T</v>
       </c>
       <c r="BL9" s="100" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>T</v>
+        <v>W</v>
       </c>
     </row>
     <row r="10" spans="1:68" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -9646,9 +9646,9 @@
         <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
-      <c r="N30" s="22">
-        <f t="shared" ca="1" si="12"/>
-        <v>2</v>
+      <c r="N30" s="22" t="str">
+        <f t="shared" ca="1" si="12"/>
+        <v/>
       </c>
       <c r="O30" s="22" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -10140,9 +10140,9 @@
         <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
-      <c r="O32" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
+      <c r="O32" s="22">
+        <f t="shared" ca="1" si="12"/>
+        <v>2</v>
       </c>
       <c r="P32" s="22" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -10220,9 +10220,9 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="AI32" s="22">
-        <f t="shared" ca="1" si="11"/>
-        <v>2</v>
+      <c r="AI32" s="22" t="str">
+        <f t="shared" ca="1" si="11"/>
+        <v/>
       </c>
       <c r="AJ32" s="22" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -11644,9 +11644,9 @@
         <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
-      <c r="V38" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
+      <c r="V38" s="22">
+        <f t="shared" ca="1" si="12"/>
+        <v>1</v>
       </c>
       <c r="W38" s="22" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -11724,9 +11724,9 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="AP38" s="22">
-        <f t="shared" ca="1" si="9"/>
-        <v>1</v>
+      <c r="AP38" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
       </c>
       <c r="AQ38" s="22" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -12065,7 +12065,7 @@
         <v>56</v>
       </c>
       <c r="E40" s="54">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F40" s="55">
         <v>46141</v>
@@ -12126,9 +12126,9 @@
         <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
-      <c r="V40" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
+      <c r="V40" s="22">
+        <f t="shared" ca="1" si="12"/>
+        <v>2</v>
       </c>
       <c r="W40" s="22" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -12206,9 +12206,9 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="AP40" s="22">
-        <f t="shared" ca="1" si="9"/>
-        <v>2</v>
+      <c r="AP40" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
       </c>
       <c r="AQ40" s="22" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -12372,9 +12372,9 @@
         <f t="shared" ca="1" si="12"/>
         <v/>
       </c>
-      <c r="V41" s="22" t="str">
-        <f t="shared" ca="1" si="12"/>
-        <v/>
+      <c r="V41" s="22">
+        <f t="shared" ca="1" si="12"/>
+        <v>2</v>
       </c>
       <c r="W41" s="22" t="str">
         <f t="shared" ca="1" si="12"/>
@@ -12452,9 +12452,9 @@
         <f t="shared" ca="1" si="9"/>
         <v/>
       </c>
-      <c r="AP41" s="22">
-        <f t="shared" ca="1" si="9"/>
-        <v>2</v>
+      <c r="AP41" s="22" t="str">
+        <f t="shared" ca="1" si="9"/>
+        <v/>
       </c>
       <c r="AQ41" s="22" t="str">
         <f t="shared" ca="1" si="9"/>
@@ -12646,9 +12646,9 @@
         <f t="shared" ca="1" si="11"/>
         <v/>
       </c>
-      <c r="AC42" s="22" t="str">
-        <f t="shared" ca="1" si="11"/>
-        <v/>
+      <c r="AC42" s="22">
+        <f t="shared" ca="1" si="11"/>
+        <v>2</v>
       </c>
       <c r="AD42" s="22" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -12726,9 +12726,9 @@
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="AW42" s="22">
+      <c r="AW42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
-        <v>2</v>
+        <v/>
       </c>
       <c r="AX42" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -13412,9 +13412,9 @@
         <f t="shared" ca="1" si="15"/>
         <v/>
       </c>
-      <c r="AJ45" s="22" t="str">
+      <c r="AJ45" s="22">
         <f t="shared" ca="1" si="15"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK45" s="22" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -13492,9 +13492,9 @@
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="BD45" s="22">
-        <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+      <c r="BD45" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
       </c>
       <c r="BE45" s="22" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -13535,7 +13535,7 @@
         <v>87</v>
       </c>
       <c r="C46" s="53" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D46" s="53" t="s">
         <v>56</v>
@@ -13932,9 +13932,9 @@
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="AQ47" s="22" t="str">
+      <c r="AQ47" s="22">
         <f t="shared" ca="1" si="14"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AR47" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -14012,9 +14012,9 @@
         <f t="shared" ca="1" si="10"/>
         <v/>
       </c>
-      <c r="BK47" s="22">
-        <f t="shared" ca="1" si="10"/>
-        <v>2</v>
+      <c r="BK47" s="22" t="str">
+        <f t="shared" ca="1" si="10"/>
+        <v/>
       </c>
       <c r="BL47" s="22" t="str">
         <f t="shared" ca="1" si="10"/>
@@ -14027,7 +14027,7 @@
         <v>88</v>
       </c>
       <c r="C48" s="53" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D48" s="53" t="s">
         <v>56</v>
@@ -14273,13 +14273,13 @@
         <v>89</v>
       </c>
       <c r="C49" s="53" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D49" s="53" t="s">
         <v>56</v>
       </c>
       <c r="E49" s="54">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F49" s="55">
         <v>46162</v>
@@ -14519,7 +14519,7 @@
         <v>90</v>
       </c>
       <c r="C50" s="53" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D50" s="53" t="s">
         <v>56</v>
@@ -14765,7 +14765,7 @@
         <v>62</v>
       </c>
       <c r="C51" s="53" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D51" s="53" t="s">
         <v>56</v>
@@ -15017,7 +15017,7 @@
         <v>56</v>
       </c>
       <c r="E52" s="54">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F52" s="55">
         <v>46169</v>
@@ -15190,9 +15190,9 @@
         <f t="shared" ca="1" si="14"/>
         <v/>
       </c>
-      <c r="AX52" s="22" t="str">
+      <c r="AX52" s="22">
         <f t="shared" ca="1" si="14"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AY52" s="22" t="str">
         <f t="shared" ca="1" si="14"/>
@@ -38113,34 +38113,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="22a266b9fa9a230c5a512669d8b298c3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eddc33fff6b14141ee5c74a0d29ea6a1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -38416,27 +38388,35 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75C87518-DD8E-42CD-8DAC-291A323E849B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -38455,4 +38435,24 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39060724-9CA2-4290-8A0C-B53624A594E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA4BA2A8-DB97-40F9-8DB6-154C09C7467C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>